--- a/providers/xtrackers/2026-07-06/xtrackers_etf_export.xlsx
+++ b/providers/xtrackers/2026-07-06/xtrackers_etf_export.xlsx
@@ -4560,7 +4560,7 @@
         <x:v>898</x:v>
       </x:c>
       <x:c r="G33" s="10">
-        <x:v>168448933.865888</x:v>
+        <x:v>170460380.88207</x:v>
       </x:c>
       <x:c r="H33" s="14" t="s">
         <x:v>902</x:v>
@@ -4583,13 +4583,13 @@
         <x:v>7.87</x:v>
       </x:c>
       <x:c r="P33" s="10">
-        <x:v>6.43</x:v>
+        <x:v>7.57</x:v>
       </x:c>
       <x:c r="Q33" s="10">
-        <x:v>10.99</x:v>
+        <x:v>13.18</x:v>
       </x:c>
       <x:c r="R33" s="12">
-        <x:v>46205</x:v>
+        <x:v>46206</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -8140,7 +8140,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="G113" s="10">
-        <x:v>50112116.04485</x:v>
+        <x:v>50239146.48313</x:v>
       </x:c>
       <x:c r="H113" s="14" t="s">
         <x:v>906</x:v>
@@ -8167,13 +8167,13 @@
         <x:v>8.89</x:v>
       </x:c>
       <x:c r="P113" s="10">
-        <x:v>4.72</x:v>
+        <x:v>4.86</x:v>
       </x:c>
       <x:c r="Q113" s="10">
-        <x:v>8.68</x:v>
+        <x:v>8.59</x:v>
       </x:c>
       <x:c r="R113" s="12">
-        <x:v>46205</x:v>
+        <x:v>46206</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -24181,7 +24181,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="G424" s="10">
-        <x:v>1730823.288681</x:v>
+        <x:v>1734740.171929</x:v>
       </x:c>
       <x:c r="H424" s="14" t="s">
         <x:v>906</x:v>
@@ -24218,7 +24218,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="G425" s="10">
-        <x:v>2659410.493326</x:v>
+        <x:v>2668866.68495</x:v>
       </x:c>
       <x:c r="H425" s="14" t="s">
         <x:v>906</x:v>
@@ -24255,7 +24255,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="G426" s="10">
-        <x:v>2948626.589172</x:v>
+        <x:v>2962648.116551</x:v>
       </x:c>
       <x:c r="H426" s="14" t="s">
         <x:v>906</x:v>
@@ -24292,7 +24292,7 @@
         <x:v>897</x:v>
       </x:c>
       <x:c r="G427" s="10">
-        <x:v>4361964.246642</x:v>
+        <x:v>4387918.296679</x:v>
       </x:c>
       <x:c r="H427" s="14" t="s">
         <x:v>906</x:v>
@@ -24975,449 +24975,449 @@
     <x:mergeCell ref="B446:R446"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink ref="B8:B8" r:id="R76c4ab14cd8e4c8d" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B9:B9" r:id="Re4e92a6942134b43" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B10:B10" r:id="R0854d3d8ec0e4b72" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B11:B11" r:id="R80ca3d7947384db7" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B12:B12" r:id="R9ae69465f36046bb" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B13:B13" r:id="R754d086787eb448e" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
-    <x:hyperlink ref="B14:B14" r:id="R900061304d074dbe" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B15:B15" r:id="Rfddb9c9810454728" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B16:B16" r:id="Recc90e2785bd471e" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B17:B17" r:id="R4c69ea827c314a7a" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B18:B18" r:id="Rc13e1c71e95b424b" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B19:B19" r:id="Rb9319b2802b14dc8" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
-    <x:hyperlink ref="B20:B20" r:id="R9a6562457deb4a74" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B21:B21" r:id="Rfdb28edc0474408a" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B22:B22" r:id="Re8ca11ef8ad04e93" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B23:B23" r:id="R538cf7289e954d9e" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
-    <x:hyperlink ref="B24:B24" r:id="R6c10710c68924746" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B25:B25" r:id="Rb098b40556eb429a" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B26:B26" r:id="Rf3744f706e6c4e75" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
-    <x:hyperlink ref="B27:B27" r:id="Rd80c5e3723c94a30" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B28:B28" r:id="Rc5dff6595f59401b" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B29:B29" r:id="R74d29c47fee242f7" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B30:B30" r:id="Rb83ff482060e4edf" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B31:B31" r:id="R849a4b109f974d62" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B32:B32" r:id="R015be9af6b4b4978" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B33:B33" r:id="R12d1660432bc4782" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B34:B34" r:id="R0036ba03983a4e18" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B35:B35" r:id="R7b45e91fee354645" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B36:B36" r:id="R3af55aa08b7a4050" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B37:B37" r:id="Refca1d68c4224411" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B38:B38" r:id="R40c84964c34e470f" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B39:B39" r:id="R8209a2ce2a3b4371" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
-    <x:hyperlink ref="B40:B40" r:id="R408ac89f5b1c4c6f" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
-    <x:hyperlink ref="B41:B41" r:id="R02782d9a6fc7488f" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B42:B42" r:id="Ra3360b10b76147cb" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B43:B43" r:id="Rc3f75c8bf51c41f8" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B44:B44" r:id="R707d972002584690" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B45:B45" r:id="R9a96a4dd99904bb8" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B46:B46" r:id="Rf3abd535d0484bb7" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B47:B47" r:id="Rb1583eb304cb4164" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B48:B48" r:id="Rea5788c8aa5d4a05" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B49:B49" r:id="Re1124f9c5fe343a2" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B50:B50" r:id="R3240a2ab4fb04505" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B51:B51" r:id="R760cfadd907a4437" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B52:B52" r:id="Rbe640890cb194f11" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B53:B53" r:id="R3c3b6fe5c4a14607" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B54:B54" r:id="R1167ef958f82485d" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B55:B55" r:id="R262e54b3d4e143f1" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
-    <x:hyperlink ref="B56:B56" r:id="R5b010130fa0a4e7a" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B57:B57" r:id="R1a0bde0356d84355" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B58:B58" r:id="R7700b23c84444f0f" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B59:B59" r:id="Rc7cf816386f14343" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B60:B60" r:id="Re6d204e22bfc4682" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B61:B61" r:id="Ra589079163b0481a" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B62:B62" r:id="Rc9ea49f0f566425c" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B63:B63" r:id="Re36f9759a5c74880" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B64:B64" r:id="R1772dea78ad24848" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
-    <x:hyperlink ref="B65:B65" r:id="Rcf7db1c2a16244c9" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B66:B66" r:id="R5d38451e47564170" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B67:B67" r:id="Racaba1a550f54967" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B68:B68" r:id="R41b7cbcaffd04aba" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B69:B69" r:id="R3875d45ca5564427" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B70:B70" r:id="R75c715bf0eab40e9" display="https://etf.dws.com//en-gb/IE000ME8PWJ4-msci-world-utilities-ucits-etf-1d/"/>
-    <x:hyperlink ref="B71:B71" r:id="R4f93f3a0f8fd4852" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B72:B72" r:id="Rd017dc1651d34098" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B73:B73" r:id="Rc4cd7ac3a78a4ffc" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B74:B74" r:id="R2aa6752540ee44f5" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B75:B75" r:id="Ra4458f84c6874576" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
-    <x:hyperlink ref="B76:B76" r:id="Rc4d865b27acb45b0" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B77:B77" r:id="Re0cdba71fdb446af" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B78:B78" r:id="R48621282abae45ab" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B79:B79" r:id="R904ec73de6b64efa" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
-    <x:hyperlink ref="B80:B80" r:id="R85aa1e5b3086408a" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B81:B81" r:id="R8ad5b81435184753" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B82:B82" r:id="R1604b76cca37468c" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B83:B83" r:id="Rcaa5a903f2a54b34" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
-    <x:hyperlink ref="B84:B84" r:id="R1be3c30053b04428" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B85:B85" r:id="R543a1caf069d450c" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B86:B86" r:id="R812c336599624bbf" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B87:B87" r:id="R60eaa2473ba442a7" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B88:B88" r:id="R495392c8f7a44329" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B89:B89" r:id="Rcb0c43dac7074247" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
-    <x:hyperlink ref="B90:B90" r:id="Rcf95589717314c33" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B91:B91" r:id="R1fb5d0e195354ebe" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B92:B92" r:id="R6adb7873ef2841ae" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B93:B93" r:id="R14bcb5ae13114378" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B94:B94" r:id="Rbf853fdffe274af4" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B95:B95" r:id="Re86fb45ada6a47ab" display="https://etf.dws.com//en-gb/IE000VCTBRW6-msci-world-industrials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B96:B96" r:id="Ra19078cbcd5446f8" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B97:B97" r:id="Rfe18b7233faf43fc" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B98:B98" r:id="R446430a37f354796" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
-    <x:hyperlink ref="B99:B99" r:id="Ra1f319a71dd54ec2" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B100:B100" r:id="R76e55a3b656040f3" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B101:B101" r:id="R80d49520987e435f" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
-    <x:hyperlink ref="B102:B102" r:id="Rd1a5ac65e7694b0a" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B103:B103" r:id="Rdf4ed86bdf1f43f8" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B104:B104" r:id="R5ac053b1d39946b1" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B105:B105" r:id="R73fac18aef294d47" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B106:B106" r:id="R4e984a5b91b244a7" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B107:B107" r:id="Rdcdeab12c0ac4e6b" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B108:B108" r:id="R1372d041d20e477f" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B109:B109" r:id="Rf35e24154e604fd3" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B110:B110" r:id="R8de8cd8188494326" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
-    <x:hyperlink ref="B111:B111" r:id="R1e372014979c45ff" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B112:B112" r:id="Rb2d4f654a0ee4090" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
-    <x:hyperlink ref="B113:B113" r:id="R4e754db8fb414677" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B114:B114" r:id="R08a8c6e6622f4762" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B115:B115" r:id="R77c319dadc894c92" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
-    <x:hyperlink ref="B116:B116" r:id="Rd0e4d98713134de8" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B117:B117" r:id="R9db637050cdd438f" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B118:B118" r:id="Rf7fcb27a419e4c43" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
-    <x:hyperlink ref="B119:B119" r:id="R352e6f238ac14dc9" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B120:B120" r:id="Rf78bceda48134eb3" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B121:B121" r:id="R9dadf563701f4cc0" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
-    <x:hyperlink ref="B122:B122" r:id="R9576a47c3837485a" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B123:B123" r:id="R2433a22fba234c9d" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B124:B124" r:id="R563aa698ec0f4241" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
-    <x:hyperlink ref="B125:B125" r:id="R1dba5bdf9f244044" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B126:B126" r:id="R2af77193f8ac439c" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B127:B127" r:id="R6b035f990b56457d" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B128:B128" r:id="Ra882c85c7d3b46a7" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
-    <x:hyperlink ref="B129:B129" r:id="R0af6706ab8f2496e" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B130:B130" r:id="R164b5c930cdf40c6" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B131:B131" r:id="R5e6703c8dc31475b" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B132:B132" r:id="R08c116dbf80c40c8" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B133:B133" r:id="Re26b4b42a3b54520" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B134:B134" r:id="Rb9a8d5d6be0f4381" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B135:B135" r:id="R7775109c165e4e6e" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
-    <x:hyperlink ref="B136:B136" r:id="R536a5b1bc41e4616" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
-    <x:hyperlink ref="B137:B137" r:id="Rd9a6040ce1e843c8" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B138:B138" r:id="R94058b27dff140d3" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B139:B139" r:id="Rcc6789bdfd9d4b38" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B140:B140" r:id="Rf7d6d919fa954f41" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B141:B141" r:id="Rdfe9466fa6aa478a" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B142:B142" r:id="R36dbb6774e104c09" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B143:B143" r:id="Re2392887dcf84666" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
-    <x:hyperlink ref="B144:B144" r:id="R229b2411878f4ee3" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
-    <x:hyperlink ref="B145:B145" r:id="R969b369dd28a4c5f" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
-    <x:hyperlink ref="B146:B146" r:id="R0c20bcfa57d24f04" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B147:B147" r:id="R73864e5506804628" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
-    <x:hyperlink ref="B148:B148" r:id="R8221e27bb9954afe" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B149:B149" r:id="R4d681fb374a1461d" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B150:B150" r:id="R9a61fa6ff4ae4b59" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B151:B151" r:id="R4ab0eced95964854" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B152:B152" r:id="R6f7dcb44ac0a49a4" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B153:B153" r:id="R1a54b378c9f84c86" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
-    <x:hyperlink ref="B154:B154" r:id="R90d1910998d641f8" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B155:B155" r:id="R5d27190af76943ce" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
-    <x:hyperlink ref="B156:B156" r:id="R59e9def06d084e37" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
-    <x:hyperlink ref="B157:B157" r:id="Rd00774d37b924628" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B158:B158" r:id="R1d222811607a4cde" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B159:B159" r:id="R8da451d32b8a4533" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
-    <x:hyperlink ref="B160:B160" r:id="R752d4d23a2d04977" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B161:B161" r:id="Rbe433ef3f9e24c95" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B162:B162" r:id="R2351014b18044cd3" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
-    <x:hyperlink ref="B163:B163" r:id="R7af9b7fd72b24838" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B164:B164" r:id="R1bac81f4186b43e2" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B165:B165" r:id="R84ddd94b1a6e436f" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B166:B166" r:id="Rbce6aa4af9d84139" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B167:B167" r:id="R2c5676c9ad464f90" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B168:B168" r:id="Radc82e0d07bb48a7" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B169:B169" r:id="R5736f123ee40484c" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B170:B170" r:id="Rde1d3102f6fe41c3" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B171:B171" r:id="Rb731774b35d9439d" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B172:B172" r:id="R1fbc8dd61fdb4c45" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B173:B173" r:id="R369d9b4f425a4fc4" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B174:B174" r:id="R692aa8c483cf48b5" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B175:B175" r:id="Refa14dbbdd9349af" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B176:B176" r:id="R5a2b580f5a974b0a" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B177:B177" r:id="R7ff615515687402d" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
-    <x:hyperlink ref="B178:B178" r:id="R3a42142250db44b0" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
-    <x:hyperlink ref="B179:B179" r:id="R0094648ef74d4721" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B180:B180" r:id="R26da78af6f234e6d" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B181:B181" r:id="Re4d638f27de1418a" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B182:B182" r:id="Rcb49147b12ab4c92" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B183:B183" r:id="R4484746ec8ed4130" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
-    <x:hyperlink ref="B184:B184" r:id="R7ddb75c0476d48f5" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B185:B185" r:id="Rc02079deee614d4c" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B186:B186" r:id="R166d6b8ea104473a" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B187:B187" r:id="Ra8c0e9f52bd14d09" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B188:B188" r:id="Rc2a1b0ff3e104edf" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B189:B189" r:id="Re26aaa4a2eca4469" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
-    <x:hyperlink ref="B190:B190" r:id="R1da1be7ee0e8444a" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
-    <x:hyperlink ref="B191:B191" r:id="Rfab49eb162a04150" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
-    <x:hyperlink ref="B192:B192" r:id="R669908ed460c4c77" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B193:B193" r:id="R5435a7c21e9c435a" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B194:B194" r:id="Rbb44f0f9cba041a0" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B195:B195" r:id="Rc95cad8e199547af" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B196:B196" r:id="Rca0ea0db4a8c484f" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B197:B197" r:id="Ree9b2d53460f411b" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B198:B198" r:id="R524c33d222f84efe" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B199:B199" r:id="R5037b4ebbbfb44a6" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
-    <x:hyperlink ref="B200:B200" r:id="R2ad01fa7ac214a0d" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B201:B201" r:id="Rd9b980728c784269" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B202:B202" r:id="R081770c49e144ca2" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
-    <x:hyperlink ref="B203:B203" r:id="Rc9a24e0680b14928" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
-    <x:hyperlink ref="B204:B204" r:id="R12b9eb024c75431d" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
-    <x:hyperlink ref="B205:B205" r:id="R711a56744e6540d8" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
-    <x:hyperlink ref="B206:B206" r:id="Rf89499244f944054" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B207:B207" r:id="Re293b13c2363498a" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B208:B208" r:id="R71e29ec3d9f84d29" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
-    <x:hyperlink ref="B209:B209" r:id="Rbafbc258efc140ed" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
-    <x:hyperlink ref="B210:B210" r:id="R87b27ab6b55f4e88" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
-    <x:hyperlink ref="B211:B211" r:id="R0164a758e4534d26" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
-    <x:hyperlink ref="B212:B212" r:id="R20b691f226fa409b" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
-    <x:hyperlink ref="B213:B213" r:id="R7edf0ffe9fa543a9" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B214:B214" r:id="R9551fc244aee49a4" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B215:B215" r:id="R27031404396c4d22" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B216:B216" r:id="R269fd4fe18b44992" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
-    <x:hyperlink ref="B217:B217" r:id="R33d31494ccef4299" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B218:B218" r:id="R26775fc7f9ce441b" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B219:B219" r:id="R7ba6e540bad84252" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
-    <x:hyperlink ref="B220:B220" r:id="R74253b8ce59b4da2" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B221:B221" r:id="R8283d2fc8e804745" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
-    <x:hyperlink ref="B222:B222" r:id="R0225f9c3bdb04686" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B223:B223" r:id="R5942cbe0ab7a4f9e" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B224:B224" r:id="R881884b1d13340d6" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B225:B225" r:id="R0ace1db50b8e4af3" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B226:B226" r:id="R24d4214d1165403e" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B227:B227" r:id="Rd85d33abf0754b32" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B228:B228" r:id="Rb5991238bf1c4495" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B229:B229" r:id="R87f8b8026e3f4d7b" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B230:B230" r:id="R9c6d97a1bd9c4343" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B231:B231" r:id="Rc4bcf018d9be44cc" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B232:B232" r:id="R5623020579a44b43" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B233:B233" r:id="R26a6d2ae61b247e2" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B234:B234" r:id="Rd208f626e59f4539" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B235:B235" r:id="R40ddcd6e7d4c44e8" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B236:B236" r:id="Re2874975cbcb4fdd" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B237:B237" r:id="R08a4a556c63c49ce" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B238:B238" r:id="Rf66f7940df534bf9" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
-    <x:hyperlink ref="B239:B239" r:id="R62c8793399c04551" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B240:B240" r:id="R19fe3dcc5483452b" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
-    <x:hyperlink ref="B241:B241" r:id="Rc347aca60d7043e2" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B242:B242" r:id="R9ce79e31972a4268" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B243:B243" r:id="Rdbec98195bd042dd" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B244:B244" r:id="Rdcf9c6bdd8a8428e" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B245:B245" r:id="Rea32ee43d2104800" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
-    <x:hyperlink ref="B246:B246" r:id="Rff61a988b6074384" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B247:B247" r:id="R9bd6cda3c4aa4aad" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
-    <x:hyperlink ref="B248:B248" r:id="Rb70a143fc2ee466f" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B249:B249" r:id="Rfefb4f01813845bf" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B250:B250" r:id="R0a4bf18c4fa14a7b" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B251:B251" r:id="R11ba89c3fd9e4c80" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B252:B252" r:id="Ra6ba66f7c54949c4" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B253:B253" r:id="Rf98d05206daa4570" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B254:B254" r:id="R1c820ef08aad4689" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B255:B255" r:id="Rae651685b738415a" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B256:B256" r:id="Rbb614d59ccbc41ca" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
-    <x:hyperlink ref="B257:B257" r:id="Ra2054ce304634394" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
-    <x:hyperlink ref="B258:B258" r:id="Re8cb2fb70dc14d43" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B259:B259" r:id="R18518587fadb4f1c" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B260:B260" r:id="Rb6c2bd59c1d34c86" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B261:B261" r:id="Rf1ff336ce9d14e7b" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B262:B262" r:id="R4185636624624240" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
-    <x:hyperlink ref="B263:B263" r:id="R6fb7b082ed1c4d57" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
-    <x:hyperlink ref="B264:B264" r:id="R3771b4343e304921" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B265:B265" r:id="Rad9dfdd95ba34168" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B266:B266" r:id="R551aa75c23bc42e1" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B267:B267" r:id="Rae3c7c9a81ac439a" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B268:B268" r:id="R9d8a59c2ba114b70" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B269:B269" r:id="R175afe9400f84a48" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
-    <x:hyperlink ref="B270:B270" r:id="R57057193d1d946a0" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B271:B271" r:id="R4560768d913f42d7" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
-    <x:hyperlink ref="B272:B272" r:id="R069535a0aada445a" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
-    <x:hyperlink ref="B273:B273" r:id="Rb20325fd59214920" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B274:B274" r:id="R3d1085d69227449a" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B275:B275" r:id="Rf51c9ec0debf4644" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
-    <x:hyperlink ref="B276:B276" r:id="Ree9c491606d44ca1" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B277:B277" r:id="R80c0fcd6bb6a4081" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B278:B278" r:id="R636d7655ba2245fc" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B279:B279" r:id="R1fe1760b3c71456d" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B280:B280" r:id="R0dbead3edbc74150" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B281:B281" r:id="R88bd093859c1441f" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B282:B282" r:id="Rc077b1c754d64dde" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B283:B283" r:id="R61654035b60542c1" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B284:B284" r:id="R5ff426cb8e1c47d6" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B285:B285" r:id="R35f1862fa8d14530" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B286:B286" r:id="Rf46134a014134c05" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B287:B287" r:id="R6131d6cb821d42dc" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
-    <x:hyperlink ref="B288:B288" r:id="Reeca93ff4f39444b" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
-    <x:hyperlink ref="B289:B289" r:id="R6fcb46aa8436484a" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B290:B290" r:id="R40d7355673cc4e89" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B291:B291" r:id="R95f39a7038974701" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B292:B292" r:id="Rcb2900f8848347f2" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
-    <x:hyperlink ref="B293:B293" r:id="R876a35992c754c63" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
-    <x:hyperlink ref="B294:B294" r:id="Rde950c8814fb4344" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B295:B295" r:id="R4f1b6241c0a04fb2" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B296:B296" r:id="Ra67926b8d2554f07" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B297:B297" r:id="Rea44367935d445d6" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
-    <x:hyperlink ref="B298:B298" r:id="R91045ff8469e4892" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B299:B299" r:id="R94bbd7479e244f1b" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B300:B300" r:id="Rf8edbf1eee9d4e56" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B301:B301" r:id="Rdf68ff5ca9584857" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B302:B302" r:id="R8ec3b76cdd624cfd" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B303:B303" r:id="Re6b0b91217e74b87" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
-    <x:hyperlink ref="B304:B304" r:id="R57f2f08a55fe4a81" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B305:B305" r:id="R537dda631e7c4ec6" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B306:B306" r:id="Rd15e551d1082498e" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
-    <x:hyperlink ref="B307:B307" r:id="R8ffbd20436324997" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
-    <x:hyperlink ref="B308:B308" r:id="R41d8353cc8154b30" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B309:B309" r:id="Rf5a55f424aa14c0e" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B310:B310" r:id="R5939f9046a574a25" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B311:B311" r:id="R16283fda281b48da" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
-    <x:hyperlink ref="B312:B312" r:id="R56bbe4c02cc34dce" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B313:B313" r:id="Rfeb31d32592a423b" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B314:B314" r:id="R2f64d0455c764bb4" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B315:B315" r:id="Rbedbd3856a2d4e49" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B316:B316" r:id="R273f7d51017e4adf" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
-    <x:hyperlink ref="B317:B317" r:id="R8d4cb02f001147e7" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
-    <x:hyperlink ref="B318:B318" r:id="R1e162a58c46f4a81" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
-    <x:hyperlink ref="B319:B319" r:id="R12f975d897454130" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B320:B320" r:id="Rc2c8a1bc3f244ee7" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B321:B321" r:id="Re293dfb60e984547" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B322:B322" r:id="Ref04917d60a24a49" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
-    <x:hyperlink ref="B323:B323" r:id="R6ee914147a924cb0" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B324:B324" r:id="Rc81e73865ffc4298" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B325:B325" r:id="R7bd8407f56a4471d" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B326:B326" r:id="R5aab1428edeb4981" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B327:B327" r:id="R1215a70be54f4db2" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B328:B328" r:id="R9f4e97e0280441f0" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
-    <x:hyperlink ref="B329:B329" r:id="R71d901d7d276447c" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B330:B330" r:id="Raf4139ef4b434f55" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B331:B331" r:id="Rf83b0f6b6d13406c" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B332:B332" r:id="R55d2a70598ea46d6" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
-    <x:hyperlink ref="B333:B333" r:id="Rc910289112f94d51" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B334:B334" r:id="R15fb6b024b34476b" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
-    <x:hyperlink ref="B335:B335" r:id="R1d8855b9b95a4c9d" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B336:B336" r:id="R1149f98375674b05" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B337:B337" r:id="Rc712910e712a4b3a" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B338:B338" r:id="R206ab492db644f9b" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
-    <x:hyperlink ref="B339:B339" r:id="R712168b67744422a" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B340:B340" r:id="Rb56f1970cd43443d" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B341:B341" r:id="Rd39988d21d1f4ac6" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
-    <x:hyperlink ref="B342:B342" r:id="R18c75e53fbf74781" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B343:B343" r:id="R36c8665f9a4c4370" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B344:B344" r:id="Rfdd53506dcae4975" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B345:B345" r:id="R0e78719fc6714c48" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
-    <x:hyperlink ref="B346:B346" r:id="Rf95d5818370741e8" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
-    <x:hyperlink ref="B347:B347" r:id="R707d0987f13d4eb8" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
-    <x:hyperlink ref="B348:B348" r:id="Rd73ab46d6db44b0a" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B349:B349" r:id="Raf33c0c393bb4e25" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B350:B350" r:id="Ra0db82d21e06446f" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B351:B351" r:id="Rc5ea372a88b04699" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B352:B352" r:id="Re562054bb9194494" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B353:B353" r:id="R37aa30623bb941be" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
-    <x:hyperlink ref="B354:B354" r:id="R32cd7ee53937491d" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B355:B355" r:id="R7e7a7bfdf9314b80" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B356:B356" r:id="R5e96d95fe40c442d" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B357:B357" r:id="Rb081b2525da04fec" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B358:B358" r:id="Ra4f8af8d531d49a2" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
-    <x:hyperlink ref="B359:B359" r:id="Ra127a84bd91a453b" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B360:B360" r:id="R25ec7e37284d405e" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
-    <x:hyperlink ref="B361:B361" r:id="R24c128b1d7d54eaf" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B362:B362" r:id="R50007dcaa7334324" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B363:B363" r:id="R6f1c81eb3c3048e8" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B364:B364" r:id="R16a1ad75f55a499d" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B365:B365" r:id="R987ef5546a844b7d" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B366:B366" r:id="Rc2399b0fc5194f9d" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B367:B367" r:id="R9efbfbe99df8404b" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B368:B368" r:id="R728c8bb0b83f4a4f" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
-    <x:hyperlink ref="B369:B369" r:id="Rbbe67422056943fa" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
-    <x:hyperlink ref="B370:B370" r:id="Rb9c5103380b84619" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
-    <x:hyperlink ref="B371:B371" r:id="R79df1f87fb764a8c" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B372:B372" r:id="Reb983092cccc42fe" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B373:B373" r:id="R05f81570fe484167" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B374:B374" r:id="R608a23b6aaac4775" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B375:B375" r:id="R250f18f04a7747b6" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B376:B376" r:id="R586420907a0a43c0" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B377:B377" r:id="R99bdf4e062e64801" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B378:B378" r:id="Rb4cebdb8080e4d7d" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B379:B379" r:id="Ra23a292f8c334ead" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B380:B380" r:id="R9a17b91d86b144fd" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B381:B381" r:id="R00602a55bda8464a" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B382:B382" r:id="Rfc972c144f404e55" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
-    <x:hyperlink ref="B383:B383" r:id="R769151a36764407d" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B384:B384" r:id="Refc5f328f3de4813" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
-    <x:hyperlink ref="B385:B385" r:id="R092757d473d549e7" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B386:B386" r:id="Rb9cb25af715740dc" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B387:B387" r:id="R38fe734a52284716" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B388:B388" r:id="Rdaf29dad79c94ffa" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B389:B389" r:id="Rb6c0120b93b4403c" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B390:B390" r:id="R9a4828b4eae246f6" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B391:B391" r:id="Rffc79ff7020c42f1" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B392:B392" r:id="R2c95715d2aab4e9e" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
-    <x:hyperlink ref="B393:B393" r:id="R9038a32a767a4775" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B394:B394" r:id="Rdb51abf2edc64616" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B395:B395" r:id="R35354641e7644bcb" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B396:B396" r:id="R7ec3ec1a1bd24f9c" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B397:B397" r:id="R4b7cb30990fd41a6" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B398:B398" r:id="R088d121dcb1042a0" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B399:B399" r:id="R0bd5e7dff87a4718" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B400:B400" r:id="R3f37198a46a943a9" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B401:B401" r:id="Racdbf9a89bce44c1" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B402:B402" r:id="Rbf2d4785b1ac4c1c" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B403:B403" r:id="Raeaae12b1a394981" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B404:B404" r:id="R0aa4d15f90504d43" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B405:B405" r:id="R34f7b9b421174d40" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B406:B406" r:id="R02ad6eeae2cf4ef7" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B407:B407" r:id="R2cd042d539814557" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B408:B408" r:id="R8c76031328e84a7d" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B409:B409" r:id="Ra56da8512b0f43e8" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B410:B410" r:id="R3564b338ca974f83" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B411:B411" r:id="R396bb4c945634e85" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
-    <x:hyperlink ref="B412:B412" r:id="Rda1004b7e0a84e3d" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B413:B413" r:id="Rfdc66c750f454a33" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B414:B414" r:id="R2326759a40f04c35" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B415:B415" r:id="Rb833f1847e6d4945" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B416:B416" r:id="R922df0cf9eb9405c" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B417:B417" r:id="Rf20f519f131f4418" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B418:B418" r:id="Rc3806ac0f9a44891" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B419:B419" r:id="R8b4893bb9e39413a" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B420:B420" r:id="R182f3d01bd7e4202" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B421:B421" r:id="R8e0904d9379b4db1" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B422:B422" r:id="R240eba85165c470f" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B423:B423" r:id="Rd2c9545b5d62456d" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
-    <x:hyperlink ref="B424:B424" r:id="R758af0ada8344d85" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B425:B425" r:id="R3fc464a3b40f4f11" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B426:B426" r:id="R4251a055f1214380" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B427:B427" r:id="Rb33848fc2231458e" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B428:B428" r:id="R4ddd4d28c3e44a49" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
-    <x:hyperlink ref="B429:B429" r:id="R10e7cb34f5804602" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B430:B430" r:id="Rb1cd7fd3600a4016" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B431:B431" r:id="Ra09e020110714dec" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B432:B432" r:id="Rbfcdcb58e74e498a" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B433:B433" r:id="R758b6070a09643be" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B434:B434" r:id="R4459c83cde3e4677" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B435:B435" r:id="Rceb4289d3af84e45" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B436:B436" r:id="R4ab7ca8326ac4663" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
-    <x:hyperlink ref="B437:B437" r:id="Rd4c1ab28eec84b37" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
-    <x:hyperlink ref="B438:B438" r:id="R0da2dd93e5e443b1" display="https://etf.dws.com//en-gb/LU3313127113-eurozone-government-bond-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B439:B439" r:id="Rfce7769384934932" display="https://etf.dws.com//en-gb/LU3353962601-msci-world-swap-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B440:B440" r:id="Rc70518b715674dd8" display="https://etf.dws.com//en-gb/LU3353962783-s-p-500-swap-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B441:B441" r:id="Rda5c8487d7cd4bfe" display="https://etf.dws.com//en-gb/LU3353962866-stoxx-global-select-dividend-100-swap-ucits-etf-ic-usd-unlisted/"/>
-    <x:hyperlink ref="B442:B442" r:id="Re790485e8182423d" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B443:B443" r:id="R1bbc7e457cb24336" display="https://etf.dws.com//en-gb/LU3370249040-bloomberg-commodity-swap-ucits-etf-3c-gbp-hedged/"/>
-    <x:hyperlink ref="B444:B444" r:id="R427ca48f0fcf435d" display="https://etf.dws.com//en-gb/LU3375213041-msci-world-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B8:B8" r:id="R8f263cb257b347fc" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B9:B9" r:id="R13f8329e9365419a" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B10:B10" r:id="R6010ca840a634f0f" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B11:B11" r:id="R6b391d1d05054f16" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B12:B12" r:id="Rb4a3e775051f40d4" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B13:B13" r:id="R868b8bc965c04d6c" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
+    <x:hyperlink ref="B14:B14" r:id="Rd57aa0aa22da440b" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B15:B15" r:id="R27337e7c109044b4" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B16:B16" r:id="R10a0bb86c78d4807" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B17:B17" r:id="Rd579a906a5d24ecf" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B18:B18" r:id="R68e87b8fcf484145" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B19:B19" r:id="R5ca24621f9b94ff1" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
+    <x:hyperlink ref="B20:B20" r:id="R41ca42ea29e64fed" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B21:B21" r:id="R254dbf785dba49c7" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B22:B22" r:id="R07768110ecc24ed4" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B23:B23" r:id="Ra39a90037114436d" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
+    <x:hyperlink ref="B24:B24" r:id="Rf0db918f9f674145" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B25:B25" r:id="R3ff85205cdc3486a" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B26:B26" r:id="R02b8fe5f71dd4ce9" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
+    <x:hyperlink ref="B27:B27" r:id="R294e9e0cdf854cb1" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B28:B28" r:id="R61ff4b4293294bb8" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B29:B29" r:id="R4c842f765d1e4c1a" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B30:B30" r:id="R59c0d7d10845440c" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B31:B31" r:id="R7ec8adfbe6d94574" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B32:B32" r:id="R793e5f2a94974471" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B33:B33" r:id="R0a91c7b9113e42e2" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B34:B34" r:id="Rc8b4be50214949a7" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B35:B35" r:id="Re65a57e8c6744803" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B36:B36" r:id="R679cad788f114ecb" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B37:B37" r:id="R6afa2d30cfbf4697" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B38:B38" r:id="R6f207a73169448d7" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B39:B39" r:id="R7a1bca3806684224" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
+    <x:hyperlink ref="B40:B40" r:id="R17d1b7906c034bea" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
+    <x:hyperlink ref="B41:B41" r:id="R7fb77754f7b64d43" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B42:B42" r:id="Rf2c56b3ba50d4e78" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B43:B43" r:id="R5d443e8f5ea048af" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B44:B44" r:id="R2970146b14924491" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B45:B45" r:id="Re31f8602f1da468b" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B46:B46" r:id="R446ae8293e6549fe" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B47:B47" r:id="R3abb3be3312841e7" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B48:B48" r:id="R69fe2ca2c2ba4c99" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B49:B49" r:id="R72c1af945b504cc2" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B50:B50" r:id="Rcaa00be0604f4ccd" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B51:B51" r:id="R58a8f79db0474b0a" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B52:B52" r:id="Rfc278b8175094ba1" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B53:B53" r:id="R0799f2d6cea1434b" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B54:B54" r:id="R4f25cbd3f2f84b91" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B55:B55" r:id="R731e3a57e0374a37" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
+    <x:hyperlink ref="B56:B56" r:id="R55edf20322d44434" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B57:B57" r:id="R2a6f7d7db71f4af6" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B58:B58" r:id="R761ddffbd1e84719" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B59:B59" r:id="R3705e4f44fd8452c" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B60:B60" r:id="Ra10ab6997fea4199" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B61:B61" r:id="R4a573083f86d4a23" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B62:B62" r:id="R4a56bd9ea0be4caf" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B63:B63" r:id="Re542488f706c4d09" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B64:B64" r:id="R19c9ea6c154b42fd" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
+    <x:hyperlink ref="B65:B65" r:id="Rf11c5575510d4360" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B66:B66" r:id="R9c265d3457e54419" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B67:B67" r:id="R59cbef0abcc5482e" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B68:B68" r:id="R13378cb01a624480" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B69:B69" r:id="Raeea215316e64a56" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B70:B70" r:id="Rb734ee3dadb941cc" display="https://etf.dws.com//en-gb/IE000ME8PWJ4-msci-world-utilities-ucits-etf-1d/"/>
+    <x:hyperlink ref="B71:B71" r:id="R429b6c73e4884ff8" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B72:B72" r:id="Rd79b65a4afcf4a70" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B73:B73" r:id="R84e907c4e3694f4b" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B74:B74" r:id="Rc2e0c0b041534bf3" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B75:B75" r:id="Rc5b9465aa22b4b5a" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
+    <x:hyperlink ref="B76:B76" r:id="Rcb8ef8c132f04e6f" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B77:B77" r:id="Rd82f3b031e2641d9" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B78:B78" r:id="R0acbc14077604e59" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B79:B79" r:id="R8c9c412ff1644225" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
+    <x:hyperlink ref="B80:B80" r:id="R86e384de86aa44fe" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B81:B81" r:id="Ra53a7b5391ae410f" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B82:B82" r:id="Rf382d3de2a934ff2" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B83:B83" r:id="Rb130db27e56c48b9" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
+    <x:hyperlink ref="B84:B84" r:id="R193dcfca53bb4b9f" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B85:B85" r:id="R052d0c192acf47f5" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B86:B86" r:id="R5346c51dd7f548e2" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B87:B87" r:id="R3e809e70e35a47f0" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B88:B88" r:id="Re715765a525d450d" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B89:B89" r:id="R6e5aa1e2df7d4d21" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
+    <x:hyperlink ref="B90:B90" r:id="R30bbfebef2e14ba7" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B91:B91" r:id="Ref42fc0a07194bb6" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B92:B92" r:id="R4a4ad8b39de14215" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B93:B93" r:id="R517bf73f87af438b" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B94:B94" r:id="R186475b0aa464130" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B95:B95" r:id="Rb15180740f2b4612" display="https://etf.dws.com//en-gb/IE000VCTBRW6-msci-world-industrials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B96:B96" r:id="R2abdc9b5695a40f8" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B97:B97" r:id="R4b79ff1f558e40c1" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B98:B98" r:id="R9f9e38bb0b3d437e" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
+    <x:hyperlink ref="B99:B99" r:id="Raa6734d7457244ed" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B100:B100" r:id="R3203d5b05fc34e2b" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B101:B101" r:id="R40806a65af9f412d" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
+    <x:hyperlink ref="B102:B102" r:id="R83daaa3fa6f741af" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B103:B103" r:id="Rbbb4813ec8ec49d2" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B104:B104" r:id="R9ab2687dcb604f2f" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B105:B105" r:id="R6a61ef010ea045a1" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B106:B106" r:id="R238dc433382d4702" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B107:B107" r:id="Rc550a42abc0f4333" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B108:B108" r:id="R46a2dff9d3db4f2b" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B109:B109" r:id="Rf5960a74b5204990" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B110:B110" r:id="R6c97e5b7277d48f8" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
+    <x:hyperlink ref="B111:B111" r:id="R773d0e03308e43ed" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B112:B112" r:id="R84e4152ab696474e" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
+    <x:hyperlink ref="B113:B113" r:id="Rc968594c012f444b" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B114:B114" r:id="R3fd928440ff141d2" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B115:B115" r:id="R913a9a66d56d46e5" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
+    <x:hyperlink ref="B116:B116" r:id="R3e1850d656094065" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B117:B117" r:id="R5ae2dbfce1094be7" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B118:B118" r:id="Ra62a62e53d504d81" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
+    <x:hyperlink ref="B119:B119" r:id="R820753d65c2f4b1b" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B120:B120" r:id="R78cb5a7079ee45aa" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B121:B121" r:id="R49dfdbcdf6b1452a" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
+    <x:hyperlink ref="B122:B122" r:id="R7229b8ad9e5046ae" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B123:B123" r:id="R7939b300d96d48de" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B124:B124" r:id="R479e037006194261" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
+    <x:hyperlink ref="B125:B125" r:id="R0e5cfac8580c41a9" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B126:B126" r:id="R60d03bf3740f40ca" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B127:B127" r:id="Rf95fc3f6cc074426" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B128:B128" r:id="R8b520c7988b84825" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
+    <x:hyperlink ref="B129:B129" r:id="Rf7574c53b4314fd1" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B130:B130" r:id="R00a287a5ebcd4fe5" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B131:B131" r:id="R3677573dcee34229" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B132:B132" r:id="R8ca17b3a99bb4597" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B133:B133" r:id="Rd7637bfcdf354ebc" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B134:B134" r:id="Rffb88724a213428f" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B135:B135" r:id="R96e9c47ad1244b6a" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
+    <x:hyperlink ref="B136:B136" r:id="R042da68d0746473f" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
+    <x:hyperlink ref="B137:B137" r:id="R871cf056f4674d5d" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B138:B138" r:id="R902af67351bd4581" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B139:B139" r:id="R2cb03ea7478d496b" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B140:B140" r:id="R8341f8f6605142a7" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B141:B141" r:id="Rbeb3cf414bbd4143" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B142:B142" r:id="R07e0c74154dc4690" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B143:B143" r:id="R779d8279ee114b09" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
+    <x:hyperlink ref="B144:B144" r:id="R5254e913cb254984" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
+    <x:hyperlink ref="B145:B145" r:id="R371cd836dab94b35" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
+    <x:hyperlink ref="B146:B146" r:id="R25cc4943ee69433d" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B147:B147" r:id="R49b1e4b1f1cb4fb1" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
+    <x:hyperlink ref="B148:B148" r:id="R42e66b74d5764fec" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B149:B149" r:id="Rd5020a9736d746b1" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B150:B150" r:id="R0a887bb98ba24a89" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B151:B151" r:id="R3e966fbee1174309" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B152:B152" r:id="R718693ded4d34a9e" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B153:B153" r:id="R0751c860cd134400" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
+    <x:hyperlink ref="B154:B154" r:id="Ra23e972323294ce8" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B155:B155" r:id="R0d0011cd86354936" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
+    <x:hyperlink ref="B156:B156" r:id="R84c9c982d9744f2d" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
+    <x:hyperlink ref="B157:B157" r:id="R1a5d3171f36641a0" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B158:B158" r:id="R8e49884ebd9741bc" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B159:B159" r:id="Ra80a9434fe7c4663" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
+    <x:hyperlink ref="B160:B160" r:id="R068a8aa2499642ef" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B161:B161" r:id="R480b39324a7a48e6" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B162:B162" r:id="R10d5d0d35ba74dcc" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
+    <x:hyperlink ref="B163:B163" r:id="R20338dbad42544f9" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B164:B164" r:id="R9beaa22335354980" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B165:B165" r:id="R6d8ba839c0a148ba" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B166:B166" r:id="R617e7293f566472f" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B167:B167" r:id="Rf25337fef6c3477a" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B168:B168" r:id="Rbbc43fa0b19b44c3" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B169:B169" r:id="R657c6cd375414107" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B170:B170" r:id="R4449d155a7fa4e4c" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B171:B171" r:id="R39719633f3834847" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B172:B172" r:id="R19b0494476144e5a" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B173:B173" r:id="R0e01b1f57dee481f" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B174:B174" r:id="R2e9d920e7c204a53" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B175:B175" r:id="R597e449e78dd4386" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B176:B176" r:id="Ra132c7516cd54443" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B177:B177" r:id="Rf67b3bc94dab4b97" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
+    <x:hyperlink ref="B178:B178" r:id="R73a4c94b8327415b" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
+    <x:hyperlink ref="B179:B179" r:id="Re97f3ba3039f4768" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B180:B180" r:id="R510b02f834864da4" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B181:B181" r:id="R620115473e3c47df" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B182:B182" r:id="Rc77e9ef974dd4537" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B183:B183" r:id="Rc186cb5ff05e44e0" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
+    <x:hyperlink ref="B184:B184" r:id="Rd0aed0e0b46941ca" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B185:B185" r:id="R68fba4e683cc48a6" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B186:B186" r:id="Rf421ae0cc77045ed" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B187:B187" r:id="R14bf85ac236b4d9d" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B188:B188" r:id="R03625e5b4c914e98" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B189:B189" r:id="R7bc5cb0957aa4b3a" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
+    <x:hyperlink ref="B190:B190" r:id="R680fc7c58f014fc9" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
+    <x:hyperlink ref="B191:B191" r:id="R9938fbaeb71c41a0" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
+    <x:hyperlink ref="B192:B192" r:id="R75fc7e15b4c04348" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B193:B193" r:id="R48389f65cfa548db" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B194:B194" r:id="Rd750ce52c1494f9c" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B195:B195" r:id="Rf5b0b38c56a04365" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B196:B196" r:id="Rbd55da4ccc1e48de" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B197:B197" r:id="R82b951f6e42e433b" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B198:B198" r:id="R1b59758203514b75" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B199:B199" r:id="R3f9602cb8efd40b0" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
+    <x:hyperlink ref="B200:B200" r:id="Rcb9e8e17ad9949ca" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B201:B201" r:id="R5fe54ee9116f4665" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B202:B202" r:id="Rc9ed9ccbbfc848c9" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
+    <x:hyperlink ref="B203:B203" r:id="R5e6f5978a0994f47" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
+    <x:hyperlink ref="B204:B204" r:id="R4a6a0d77af9d4ba4" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
+    <x:hyperlink ref="B205:B205" r:id="R46c668b7f5bf428d" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
+    <x:hyperlink ref="B206:B206" r:id="R2cc89b2a3fb74094" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B207:B207" r:id="R524a820e1c2a4e14" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B208:B208" r:id="R12928de54b6c4424" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
+    <x:hyperlink ref="B209:B209" r:id="R56f8a65f48404aaf" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
+    <x:hyperlink ref="B210:B210" r:id="Ra0c58e30eb6d4c21" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
+    <x:hyperlink ref="B211:B211" r:id="R14c5406170dd490b" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
+    <x:hyperlink ref="B212:B212" r:id="R5839ba169f5d40bb" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
+    <x:hyperlink ref="B213:B213" r:id="R46885ccef3ae4254" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B214:B214" r:id="R4935812bdfc745ea" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B215:B215" r:id="Rebc7f218081f47fc" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B216:B216" r:id="Rf097c6fba1734e81" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
+    <x:hyperlink ref="B217:B217" r:id="Rde59889c5ab44270" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B218:B218" r:id="R10df4ffc76094846" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B219:B219" r:id="R9de0b9a4ca6545aa" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
+    <x:hyperlink ref="B220:B220" r:id="Ra0d8fb0d1d144366" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B221:B221" r:id="R5b66256e05e24315" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
+    <x:hyperlink ref="B222:B222" r:id="R826268743d5743ef" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B223:B223" r:id="R3486afef020c4f86" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B224:B224" r:id="R0c6eea39d2f046be" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B225:B225" r:id="R92f70d8c725a42a2" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B226:B226" r:id="R2f375f7f74ad4a15" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B227:B227" r:id="R7a9038ebad414db3" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B228:B228" r:id="R4d796f2ad61f429b" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B229:B229" r:id="Ra1684f3f9e474603" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B230:B230" r:id="R38ae47fc384b4fd7" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B231:B231" r:id="R510ac10d1cf249ae" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B232:B232" r:id="Rb0549fd10f03469a" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B233:B233" r:id="Rce08a2f8ae074b5b" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B234:B234" r:id="R032245f499a04f76" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B235:B235" r:id="R3d867b1e70ba4b08" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B236:B236" r:id="R8056789d293444a1" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B237:B237" r:id="R975d4d3be82842ae" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B238:B238" r:id="R28973b988b9241b0" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
+    <x:hyperlink ref="B239:B239" r:id="R011a19d645a349d3" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B240:B240" r:id="R26703f2e438246e6" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
+    <x:hyperlink ref="B241:B241" r:id="Rcd84dd56d1e147c9" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B242:B242" r:id="R93e6f93cde894323" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B243:B243" r:id="Rca97b442bb644bca" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B244:B244" r:id="R2986ac8ec96c49d0" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B245:B245" r:id="Rddcf2afa2686411e" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
+    <x:hyperlink ref="B246:B246" r:id="R7d005f84fc2e475f" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B247:B247" r:id="R59b7557741ce4143" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
+    <x:hyperlink ref="B248:B248" r:id="Rbfe1f024a7314553" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B249:B249" r:id="Rfa6350ed19324933" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B250:B250" r:id="Rf9a9a9f227b64093" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B251:B251" r:id="Rd6ed3a9b2e134a6c" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B252:B252" r:id="R22b0a96e41894b5e" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B253:B253" r:id="Rf5bd8be242d04b76" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B254:B254" r:id="R366319d1af714d0f" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B255:B255" r:id="R5d55f43bc4ee4ac7" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B256:B256" r:id="R080b9e4369b7413d" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
+    <x:hyperlink ref="B257:B257" r:id="R1846206d29e4403a" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
+    <x:hyperlink ref="B258:B258" r:id="R56fa2ce159e44eb8" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B259:B259" r:id="R98eae38991f24b8b" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B260:B260" r:id="Rdcc770c670284196" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B261:B261" r:id="Ra3a2283ad12d48ee" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B262:B262" r:id="R5db9f7a7b96c4d1f" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
+    <x:hyperlink ref="B263:B263" r:id="R92a71e0d71694efa" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
+    <x:hyperlink ref="B264:B264" r:id="R22097a3152144bae" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B265:B265" r:id="R728e2b69ffdf4409" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B266:B266" r:id="R5b951a31423043fb" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B267:B267" r:id="Rcf41fe6d38b94d20" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B268:B268" r:id="Rd12bfe23a0ca4277" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B269:B269" r:id="R7cca275932454c3b" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
+    <x:hyperlink ref="B270:B270" r:id="R2a8234996567409d" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B271:B271" r:id="Rf6beec0f024f484f" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
+    <x:hyperlink ref="B272:B272" r:id="R251f2906477b4cc2" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
+    <x:hyperlink ref="B273:B273" r:id="Rbcb09db47da74123" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B274:B274" r:id="Rb0db9618a93d426c" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B275:B275" r:id="R25c7047c33174312" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
+    <x:hyperlink ref="B276:B276" r:id="Rad147535aaf24d45" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B277:B277" r:id="R54c9b5c389634627" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B278:B278" r:id="R1fb9d6ad8ec94cd2" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B279:B279" r:id="R8b5bdcf4ca7647d7" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B280:B280" r:id="R4ea2856778cb41be" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B281:B281" r:id="R2b32f10ce3c44ad1" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B282:B282" r:id="R84cf3d96da834dcf" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B283:B283" r:id="R3d429849df774ab0" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B284:B284" r:id="R6a1989db4e614e27" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B285:B285" r:id="Ra356f9ac5cc24e58" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B286:B286" r:id="R8865b451480041ef" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B287:B287" r:id="Ra7133365f9c54d03" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
+    <x:hyperlink ref="B288:B288" r:id="R75c0730242a54a68" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
+    <x:hyperlink ref="B289:B289" r:id="Rbf1223eff5354e82" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B290:B290" r:id="R071355f934e34725" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B291:B291" r:id="Rc75460583d3b4c0b" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B292:B292" r:id="R748e3bb6a42d4eaf" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
+    <x:hyperlink ref="B293:B293" r:id="Rbacb36ea22d64c61" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
+    <x:hyperlink ref="B294:B294" r:id="Rd325bfddb3904d88" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B295:B295" r:id="R4b053248269441c7" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B296:B296" r:id="Rf8f7504a4ab04943" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B297:B297" r:id="R3d21ca378ccb49bd" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
+    <x:hyperlink ref="B298:B298" r:id="R3d6c143b14634e24" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B299:B299" r:id="R16898b23ca5f4f52" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B300:B300" r:id="R1fc611531d334a04" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B301:B301" r:id="Rde9519e745c54842" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B302:B302" r:id="R46ef2e77e68d4a0b" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B303:B303" r:id="R746104b3879a4bbb" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
+    <x:hyperlink ref="B304:B304" r:id="Rcf19faa6c2334c86" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B305:B305" r:id="R4ded5ee2b6214dbc" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B306:B306" r:id="R0b647a2476fc4151" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
+    <x:hyperlink ref="B307:B307" r:id="Rcd6ac00533224fc2" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
+    <x:hyperlink ref="B308:B308" r:id="R3db9e3670abe43c2" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B309:B309" r:id="Rf342b4bf4e8e405b" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B310:B310" r:id="R448b2c159eab4d8d" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B311:B311" r:id="R9f9b41d71fae46c6" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
+    <x:hyperlink ref="B312:B312" r:id="R0614a9fa0af2423d" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B313:B313" r:id="Rc4436eee38734b91" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B314:B314" r:id="Rdc276cf99ca24eab" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B315:B315" r:id="Rf307df2f7b2a4066" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B316:B316" r:id="R641e4cd2e6274508" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
+    <x:hyperlink ref="B317:B317" r:id="R01e0b83bd5d148a5" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
+    <x:hyperlink ref="B318:B318" r:id="R3047ed6d5e2340ec" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
+    <x:hyperlink ref="B319:B319" r:id="R8cd769e5de1b4fda" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B320:B320" r:id="R1096ab1023244d9d" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B321:B321" r:id="Rdf93a80bc19946ce" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B322:B322" r:id="R141b3ad4dfcd4b59" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
+    <x:hyperlink ref="B323:B323" r:id="R5d34c056d76b4090" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B324:B324" r:id="R19585aab27bf4b93" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B325:B325" r:id="R440a1436d5ea49bd" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B326:B326" r:id="R599c292a3c674f82" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B327:B327" r:id="R832aa5ee49ee47d6" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B328:B328" r:id="Rc195d51cd1a54ade" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
+    <x:hyperlink ref="B329:B329" r:id="Rf3a646a59b6d4f67" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B330:B330" r:id="R2dea5588b2fa4804" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B331:B331" r:id="R44affc83d8914e2a" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B332:B332" r:id="R9a76b2cfb8424a98" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
+    <x:hyperlink ref="B333:B333" r:id="Rbf761dfc36024f72" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B334:B334" r:id="Rc994257a33ab45a8" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
+    <x:hyperlink ref="B335:B335" r:id="R7fc5f3382f25401f" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B336:B336" r:id="Rf0992d85a19347ab" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B337:B337" r:id="R7e5d838f4ac04cae" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B338:B338" r:id="R0e5931284bcb4e61" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
+    <x:hyperlink ref="B339:B339" r:id="R5d854ea4806e4d21" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B340:B340" r:id="Re0bd68eb29874a7b" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B341:B341" r:id="R219f95b0e92b4721" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
+    <x:hyperlink ref="B342:B342" r:id="R3d7c8fb1c06845d1" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B343:B343" r:id="Rc2d8ebbf10fa40b0" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B344:B344" r:id="Rb0c1bbcb2c0c4422" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B345:B345" r:id="R3322fca9fd794062" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
+    <x:hyperlink ref="B346:B346" r:id="R728da9b750094e7a" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
+    <x:hyperlink ref="B347:B347" r:id="R09904bfa2df14656" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
+    <x:hyperlink ref="B348:B348" r:id="Re2c2750295c14a7c" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B349:B349" r:id="Radfd415056ee4034" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B350:B350" r:id="R7419805829e54429" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B351:B351" r:id="R636a264a32e74081" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B352:B352" r:id="R9b1fba3342eb49a7" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B353:B353" r:id="Rdde2947532944ca1" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
+    <x:hyperlink ref="B354:B354" r:id="Re57efb25ce4a4159" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B355:B355" r:id="Rfd8e4831be5344d1" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B356:B356" r:id="R51822c21cd544ed6" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B357:B357" r:id="R4f194c994f744ff3" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B358:B358" r:id="Rc764c5e7aa36469e" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
+    <x:hyperlink ref="B359:B359" r:id="Rba0b61ab6c0e4642" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B360:B360" r:id="Re6b6808eb3dc4f8d" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
+    <x:hyperlink ref="B361:B361" r:id="Rb99419e7f78e4736" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B362:B362" r:id="R2d0e820a2e45490e" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B363:B363" r:id="R9a5775c677654751" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B364:B364" r:id="R9a980f06bea649ff" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B365:B365" r:id="R278a669a73b24dd7" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B366:B366" r:id="R89e7cbf842684e45" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B367:B367" r:id="Rcb2e76d3a1de4b97" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B368:B368" r:id="Re1617e483c3542c6" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
+    <x:hyperlink ref="B369:B369" r:id="Rbc6080c223c24836" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
+    <x:hyperlink ref="B370:B370" r:id="Rc242366d06f1435c" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
+    <x:hyperlink ref="B371:B371" r:id="R8962c685e8ec4c25" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B372:B372" r:id="Rf0d3c50cfb834e29" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B373:B373" r:id="R413daee19dd44819" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B374:B374" r:id="Ree447bf4b8504ef2" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B375:B375" r:id="R15fe11a318dc49d7" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B376:B376" r:id="R3f5b4676a0b5423e" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B377:B377" r:id="Rd42b88ac1e454627" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B378:B378" r:id="Rd5d96a7eef434983" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B379:B379" r:id="R15416d14c50d48c3" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B380:B380" r:id="Rb0985b2bb4d84ca7" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B381:B381" r:id="R4e3e298a8d41453a" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B382:B382" r:id="Re1c620db5886426c" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
+    <x:hyperlink ref="B383:B383" r:id="Rc21ce8810c974f10" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B384:B384" r:id="Rdcfcf52cce4640d9" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
+    <x:hyperlink ref="B385:B385" r:id="Rf07c4b1246354a40" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B386:B386" r:id="Rbe65dec7150a466c" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B387:B387" r:id="R4a5e06d9ef1b4662" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B388:B388" r:id="R5e2bd8121d0d452e" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B389:B389" r:id="Rbacf8862d9e24f58" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B390:B390" r:id="R619d7b0f63734ae6" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B391:B391" r:id="R5d3c7ac0033a41ba" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B392:B392" r:id="R9c12c86a138143f2" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
+    <x:hyperlink ref="B393:B393" r:id="Raba44841302548f6" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B394:B394" r:id="R0d43a25057784e7a" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B395:B395" r:id="Ra5c53c1c852d464c" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B396:B396" r:id="Ra286b76f55f1496d" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B397:B397" r:id="R2f424c67c3bb41bd" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B398:B398" r:id="Rfc86f0b3fc1d4ff9" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B399:B399" r:id="R8ed35939e23d43cd" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B400:B400" r:id="R2ad4db2fd11d46ac" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B401:B401" r:id="Rfd45266cbfba49c1" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B402:B402" r:id="R0665a7443a0641e8" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B403:B403" r:id="Re80f963180ab4daf" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B404:B404" r:id="R610e108dc452477d" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B405:B405" r:id="R88c41e6d9d4a496f" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B406:B406" r:id="R7e18efe334484f34" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B407:B407" r:id="Rc7caec1334cf4ebb" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B408:B408" r:id="R57f0ab895b464368" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B409:B409" r:id="Rb1cd2557f51346d3" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B410:B410" r:id="R2378f41f49984307" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B411:B411" r:id="R9eece941920441fc" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
+    <x:hyperlink ref="B412:B412" r:id="R2205987ec4254c9d" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B413:B413" r:id="R6db297799e2e4a80" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B414:B414" r:id="R487aae73b6094ef9" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B415:B415" r:id="R52ff9c8405aa40ac" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B416:B416" r:id="Rdfa572bcab0f49ba" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B417:B417" r:id="Rdc5d7aae88d34284" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B418:B418" r:id="R39ebf6d08f9b4fde" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B419:B419" r:id="Rd781ecb496a64504" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B420:B420" r:id="R02a4f3aaa73748fa" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B421:B421" r:id="R8376088d3562420f" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B422:B422" r:id="R7999153050c149cc" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B423:B423" r:id="R5312134eb8084d88" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
+    <x:hyperlink ref="B424:B424" r:id="R31572fc1a0e3484d" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B425:B425" r:id="Rf1ae8fb1174a4e22" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B426:B426" r:id="R39626255a5f0446a" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B427:B427" r:id="R4f7762e300e541ba" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B428:B428" r:id="Rdaab7e3a44804f8e" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
+    <x:hyperlink ref="B429:B429" r:id="R79d7340726b646a1" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B430:B430" r:id="Rb22c65a33a444540" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B431:B431" r:id="Rc32fe4389d634c0b" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B432:B432" r:id="Re84d4772ce7f4cdd" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B433:B433" r:id="R935bb767c3674252" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B434:B434" r:id="R3f46ac4a2f1e40da" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B435:B435" r:id="Rffe53a336ef04281" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B436:B436" r:id="R5c81c47cab984378" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B437:B437" r:id="R507920d9c2d54456" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
+    <x:hyperlink ref="B438:B438" r:id="Rb856c83270e14e4a" display="https://etf.dws.com//en-gb/LU3313127113-eurozone-government-bond-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B439:B439" r:id="R5729e003b3ce4c7f" display="https://etf.dws.com//en-gb/LU3353962601-msci-world-swap-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B440:B440" r:id="Rbbc91e1fe8244902" display="https://etf.dws.com//en-gb/LU3353962783-s-p-500-swap-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B441:B441" r:id="Rc56491d0f3a24a56" display="https://etf.dws.com//en-gb/LU3353962866-stoxx-global-select-dividend-100-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B442:B442" r:id="R2461d218ce4e4e6a" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B443:B443" r:id="Rc537e786ca474655" display="https://etf.dws.com//en-gb/LU3370249040-bloomberg-commodity-swap-ucits-etf-3c-gbp-hedged/"/>
+    <x:hyperlink ref="B444:B444" r:id="Rb70219e3a88b4ab0" display="https://etf.dws.com//en-gb/LU3375213041-msci-world-swap-ucits-etf-ic-usd-unlisted/"/>
   </x:hyperlinks>
   <x:pageMargins left="0.17" right="0.17" top="0.17" bottom="0.17" header="0" footer="0.3"/>
   <x:pageSetup orientation="landscape"/>
   <x:drawing r:id="rId2"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R825a961dd51b41e1"/>
+    <x:tablePart r:id="R72755efb6d20477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/providers/xtrackers/2026-07-06/xtrackers_etf_export.xlsx
+++ b/providers/xtrackers/2026-07-06/xtrackers_etf_export.xlsx
@@ -24975,449 +24975,449 @@
     <x:mergeCell ref="B446:R446"/>
   </x:mergeCells>
   <x:hyperlinks>
-    <x:hyperlink ref="B8:B8" r:id="R8f263cb257b347fc" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B9:B9" r:id="R13f8329e9365419a" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B10:B10" r:id="R6010ca840a634f0f" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B11:B11" r:id="R6b391d1d05054f16" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B12:B12" r:id="Rb4a3e775051f40d4" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B13:B13" r:id="R868b8bc965c04d6c" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
-    <x:hyperlink ref="B14:B14" r:id="Rd57aa0aa22da440b" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B15:B15" r:id="R27337e7c109044b4" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B16:B16" r:id="R10a0bb86c78d4807" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B17:B17" r:id="Rd579a906a5d24ecf" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B18:B18" r:id="R68e87b8fcf484145" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B19:B19" r:id="R5ca24621f9b94ff1" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
-    <x:hyperlink ref="B20:B20" r:id="R41ca42ea29e64fed" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B21:B21" r:id="R254dbf785dba49c7" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B22:B22" r:id="R07768110ecc24ed4" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B23:B23" r:id="Ra39a90037114436d" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
-    <x:hyperlink ref="B24:B24" r:id="Rf0db918f9f674145" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B25:B25" r:id="R3ff85205cdc3486a" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B26:B26" r:id="R02b8fe5f71dd4ce9" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
-    <x:hyperlink ref="B27:B27" r:id="R294e9e0cdf854cb1" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B28:B28" r:id="R61ff4b4293294bb8" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B29:B29" r:id="R4c842f765d1e4c1a" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B30:B30" r:id="R59c0d7d10845440c" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B31:B31" r:id="R7ec8adfbe6d94574" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B32:B32" r:id="R793e5f2a94974471" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B33:B33" r:id="R0a91c7b9113e42e2" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B34:B34" r:id="Rc8b4be50214949a7" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B35:B35" r:id="Re65a57e8c6744803" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B36:B36" r:id="R679cad788f114ecb" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B37:B37" r:id="R6afa2d30cfbf4697" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B38:B38" r:id="R6f207a73169448d7" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B39:B39" r:id="R7a1bca3806684224" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
-    <x:hyperlink ref="B40:B40" r:id="R17d1b7906c034bea" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
-    <x:hyperlink ref="B41:B41" r:id="R7fb77754f7b64d43" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B42:B42" r:id="Rf2c56b3ba50d4e78" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B43:B43" r:id="R5d443e8f5ea048af" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B44:B44" r:id="R2970146b14924491" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B45:B45" r:id="Re31f8602f1da468b" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B46:B46" r:id="R446ae8293e6549fe" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B47:B47" r:id="R3abb3be3312841e7" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B48:B48" r:id="R69fe2ca2c2ba4c99" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B49:B49" r:id="R72c1af945b504cc2" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B50:B50" r:id="Rcaa00be0604f4ccd" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B51:B51" r:id="R58a8f79db0474b0a" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B52:B52" r:id="Rfc278b8175094ba1" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B53:B53" r:id="R0799f2d6cea1434b" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
-    <x:hyperlink ref="B54:B54" r:id="R4f25cbd3f2f84b91" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B55:B55" r:id="R731e3a57e0374a37" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
-    <x:hyperlink ref="B56:B56" r:id="R55edf20322d44434" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
-    <x:hyperlink ref="B57:B57" r:id="R2a6f7d7db71f4af6" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B58:B58" r:id="R761ddffbd1e84719" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B59:B59" r:id="R3705e4f44fd8452c" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B60:B60" r:id="Ra10ab6997fea4199" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B61:B61" r:id="R4a573083f86d4a23" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B62:B62" r:id="R4a56bd9ea0be4caf" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B63:B63" r:id="Re542488f706c4d09" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B64:B64" r:id="R19c9ea6c154b42fd" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
-    <x:hyperlink ref="B65:B65" r:id="Rf11c5575510d4360" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B66:B66" r:id="R9c265d3457e54419" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B67:B67" r:id="R59cbef0abcc5482e" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
-    <x:hyperlink ref="B68:B68" r:id="R13378cb01a624480" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B69:B69" r:id="Raeea215316e64a56" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B70:B70" r:id="Rb734ee3dadb941cc" display="https://etf.dws.com//en-gb/IE000ME8PWJ4-msci-world-utilities-ucits-etf-1d/"/>
-    <x:hyperlink ref="B71:B71" r:id="R429b6c73e4884ff8" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B72:B72" r:id="Rd79b65a4afcf4a70" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B73:B73" r:id="R84e907c4e3694f4b" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B74:B74" r:id="Rc2e0c0b041534bf3" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B75:B75" r:id="Rc5b9465aa22b4b5a" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
-    <x:hyperlink ref="B76:B76" r:id="Rcb8ef8c132f04e6f" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B77:B77" r:id="Rd82f3b031e2641d9" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B78:B78" r:id="R0acbc14077604e59" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
-    <x:hyperlink ref="B79:B79" r:id="R8c9c412ff1644225" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
-    <x:hyperlink ref="B80:B80" r:id="R86e384de86aa44fe" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B81:B81" r:id="Ra53a7b5391ae410f" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B82:B82" r:id="Rf382d3de2a934ff2" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B83:B83" r:id="Rb130db27e56c48b9" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
-    <x:hyperlink ref="B84:B84" r:id="R193dcfca53bb4b9f" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B85:B85" r:id="R052d0c192acf47f5" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B86:B86" r:id="R5346c51dd7f548e2" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B87:B87" r:id="R3e809e70e35a47f0" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B88:B88" r:id="Re715765a525d450d" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B89:B89" r:id="R6e5aa1e2df7d4d21" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
-    <x:hyperlink ref="B90:B90" r:id="R30bbfebef2e14ba7" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B91:B91" r:id="Ref42fc0a07194bb6" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B92:B92" r:id="R4a4ad8b39de14215" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B93:B93" r:id="R517bf73f87af438b" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B94:B94" r:id="R186475b0aa464130" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B95:B95" r:id="Rb15180740f2b4612" display="https://etf.dws.com//en-gb/IE000VCTBRW6-msci-world-industrials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B96:B96" r:id="R2abdc9b5695a40f8" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B97:B97" r:id="R4b79ff1f558e40c1" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
-    <x:hyperlink ref="B98:B98" r:id="R9f9e38bb0b3d437e" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
-    <x:hyperlink ref="B99:B99" r:id="Raa6734d7457244ed" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B100:B100" r:id="R3203d5b05fc34e2b" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B101:B101" r:id="R40806a65af9f412d" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
-    <x:hyperlink ref="B102:B102" r:id="R83daaa3fa6f741af" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
-    <x:hyperlink ref="B103:B103" r:id="Rbbb4813ec8ec49d2" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B104:B104" r:id="R9ab2687dcb604f2f" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B105:B105" r:id="R6a61ef010ea045a1" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B106:B106" r:id="R238dc433382d4702" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B107:B107" r:id="Rc550a42abc0f4333" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
-    <x:hyperlink ref="B108:B108" r:id="R46a2dff9d3db4f2b" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B109:B109" r:id="Rf5960a74b5204990" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
-    <x:hyperlink ref="B110:B110" r:id="R6c97e5b7277d48f8" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
-    <x:hyperlink ref="B111:B111" r:id="R773d0e03308e43ed" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B112:B112" r:id="R84e4152ab696474e" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
-    <x:hyperlink ref="B113:B113" r:id="Rc968594c012f444b" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B114:B114" r:id="R3fd928440ff141d2" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B115:B115" r:id="R913a9a66d56d46e5" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
-    <x:hyperlink ref="B116:B116" r:id="R3e1850d656094065" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B117:B117" r:id="R5ae2dbfce1094be7" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B118:B118" r:id="Ra62a62e53d504d81" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
-    <x:hyperlink ref="B119:B119" r:id="R820753d65c2f4b1b" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B120:B120" r:id="R78cb5a7079ee45aa" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
-    <x:hyperlink ref="B121:B121" r:id="R49dfdbcdf6b1452a" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
-    <x:hyperlink ref="B122:B122" r:id="R7229b8ad9e5046ae" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B123:B123" r:id="R7939b300d96d48de" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B124:B124" r:id="R479e037006194261" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
-    <x:hyperlink ref="B125:B125" r:id="R0e5cfac8580c41a9" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B126:B126" r:id="R60d03bf3740f40ca" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B127:B127" r:id="Rf95fc3f6cc074426" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B128:B128" r:id="R8b520c7988b84825" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
-    <x:hyperlink ref="B129:B129" r:id="Rf7574c53b4314fd1" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B130:B130" r:id="R00a287a5ebcd4fe5" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B131:B131" r:id="R3677573dcee34229" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B132:B132" r:id="R8ca17b3a99bb4597" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B133:B133" r:id="Rd7637bfcdf354ebc" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B134:B134" r:id="Rffb88724a213428f" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B135:B135" r:id="R96e9c47ad1244b6a" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
-    <x:hyperlink ref="B136:B136" r:id="R042da68d0746473f" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
-    <x:hyperlink ref="B137:B137" r:id="R871cf056f4674d5d" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B138:B138" r:id="R902af67351bd4581" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B139:B139" r:id="R2cb03ea7478d496b" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B140:B140" r:id="R8341f8f6605142a7" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B141:B141" r:id="Rbeb3cf414bbd4143" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B142:B142" r:id="R07e0c74154dc4690" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B143:B143" r:id="R779d8279ee114b09" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
-    <x:hyperlink ref="B144:B144" r:id="R5254e913cb254984" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
-    <x:hyperlink ref="B145:B145" r:id="R371cd836dab94b35" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
-    <x:hyperlink ref="B146:B146" r:id="R25cc4943ee69433d" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B147:B147" r:id="R49b1e4b1f1cb4fb1" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
-    <x:hyperlink ref="B148:B148" r:id="R42e66b74d5764fec" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B149:B149" r:id="Rd5020a9736d746b1" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B150:B150" r:id="R0a887bb98ba24a89" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
-    <x:hyperlink ref="B151:B151" r:id="R3e966fbee1174309" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
-    <x:hyperlink ref="B152:B152" r:id="R718693ded4d34a9e" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B153:B153" r:id="R0751c860cd134400" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
-    <x:hyperlink ref="B154:B154" r:id="Ra23e972323294ce8" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
-    <x:hyperlink ref="B155:B155" r:id="R0d0011cd86354936" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
-    <x:hyperlink ref="B156:B156" r:id="R84c9c982d9744f2d" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
-    <x:hyperlink ref="B157:B157" r:id="R1a5d3171f36641a0" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B158:B158" r:id="R8e49884ebd9741bc" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
-    <x:hyperlink ref="B159:B159" r:id="Ra80a9434fe7c4663" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
-    <x:hyperlink ref="B160:B160" r:id="R068a8aa2499642ef" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B161:B161" r:id="R480b39324a7a48e6" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B162:B162" r:id="R10d5d0d35ba74dcc" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
-    <x:hyperlink ref="B163:B163" r:id="R20338dbad42544f9" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B164:B164" r:id="R9beaa22335354980" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B165:B165" r:id="R6d8ba839c0a148ba" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B166:B166" r:id="R617e7293f566472f" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
-    <x:hyperlink ref="B167:B167" r:id="Rf25337fef6c3477a" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B168:B168" r:id="Rbbc43fa0b19b44c3" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
-    <x:hyperlink ref="B169:B169" r:id="R657c6cd375414107" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B170:B170" r:id="R4449d155a7fa4e4c" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B171:B171" r:id="R39719633f3834847" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B172:B172" r:id="R19b0494476144e5a" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B173:B173" r:id="R0e01b1f57dee481f" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B174:B174" r:id="R2e9d920e7c204a53" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B175:B175" r:id="R597e449e78dd4386" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B176:B176" r:id="Ra132c7516cd54443" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B177:B177" r:id="Rf67b3bc94dab4b97" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
-    <x:hyperlink ref="B178:B178" r:id="R73a4c94b8327415b" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
-    <x:hyperlink ref="B179:B179" r:id="Re97f3ba3039f4768" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B180:B180" r:id="R510b02f834864da4" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B181:B181" r:id="R620115473e3c47df" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B182:B182" r:id="Rc77e9ef974dd4537" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B183:B183" r:id="Rc186cb5ff05e44e0" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
-    <x:hyperlink ref="B184:B184" r:id="Rd0aed0e0b46941ca" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
-    <x:hyperlink ref="B185:B185" r:id="R68fba4e683cc48a6" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B186:B186" r:id="Rf421ae0cc77045ed" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B187:B187" r:id="R14bf85ac236b4d9d" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B188:B188" r:id="R03625e5b4c914e98" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B189:B189" r:id="R7bc5cb0957aa4b3a" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
-    <x:hyperlink ref="B190:B190" r:id="R680fc7c58f014fc9" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
-    <x:hyperlink ref="B191:B191" r:id="R9938fbaeb71c41a0" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
-    <x:hyperlink ref="B192:B192" r:id="R75fc7e15b4c04348" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B193:B193" r:id="R48389f65cfa548db" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B194:B194" r:id="Rd750ce52c1494f9c" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
-    <x:hyperlink ref="B195:B195" r:id="Rf5b0b38c56a04365" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B196:B196" r:id="Rbd55da4ccc1e48de" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B197:B197" r:id="R82b951f6e42e433b" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B198:B198" r:id="R1b59758203514b75" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B199:B199" r:id="R3f9602cb8efd40b0" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
-    <x:hyperlink ref="B200:B200" r:id="Rcb9e8e17ad9949ca" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B201:B201" r:id="R5fe54ee9116f4665" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B202:B202" r:id="Rc9ed9ccbbfc848c9" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
-    <x:hyperlink ref="B203:B203" r:id="R5e6f5978a0994f47" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
-    <x:hyperlink ref="B204:B204" r:id="R4a6a0d77af9d4ba4" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
-    <x:hyperlink ref="B205:B205" r:id="R46c668b7f5bf428d" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
-    <x:hyperlink ref="B206:B206" r:id="R2cc89b2a3fb74094" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B207:B207" r:id="R524a820e1c2a4e14" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B208:B208" r:id="R12928de54b6c4424" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
-    <x:hyperlink ref="B209:B209" r:id="R56f8a65f48404aaf" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
-    <x:hyperlink ref="B210:B210" r:id="Ra0c58e30eb6d4c21" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
-    <x:hyperlink ref="B211:B211" r:id="R14c5406170dd490b" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
-    <x:hyperlink ref="B212:B212" r:id="R5839ba169f5d40bb" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
-    <x:hyperlink ref="B213:B213" r:id="R46885ccef3ae4254" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B214:B214" r:id="R4935812bdfc745ea" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B215:B215" r:id="Rebc7f218081f47fc" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B216:B216" r:id="Rf097c6fba1734e81" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
-    <x:hyperlink ref="B217:B217" r:id="Rde59889c5ab44270" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B218:B218" r:id="R10df4ffc76094846" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
-    <x:hyperlink ref="B219:B219" r:id="R9de0b9a4ca6545aa" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
-    <x:hyperlink ref="B220:B220" r:id="Ra0d8fb0d1d144366" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
-    <x:hyperlink ref="B221:B221" r:id="R5b66256e05e24315" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
-    <x:hyperlink ref="B222:B222" r:id="R826268743d5743ef" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B223:B223" r:id="R3486afef020c4f86" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
-    <x:hyperlink ref="B224:B224" r:id="R0c6eea39d2f046be" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B225:B225" r:id="R92f70d8c725a42a2" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
-    <x:hyperlink ref="B226:B226" r:id="R2f375f7f74ad4a15" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
-    <x:hyperlink ref="B227:B227" r:id="R7a9038ebad414db3" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
-    <x:hyperlink ref="B228:B228" r:id="R4d796f2ad61f429b" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
-    <x:hyperlink ref="B229:B229" r:id="Ra1684f3f9e474603" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
-    <x:hyperlink ref="B230:B230" r:id="R38ae47fc384b4fd7" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B231:B231" r:id="R510ac10d1cf249ae" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B232:B232" r:id="Rb0549fd10f03469a" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B233:B233" r:id="Rce08a2f8ae074b5b" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B234:B234" r:id="R032245f499a04f76" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B235:B235" r:id="R3d867b1e70ba4b08" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B236:B236" r:id="R8056789d293444a1" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B237:B237" r:id="R975d4d3be82842ae" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B238:B238" r:id="R28973b988b9241b0" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
-    <x:hyperlink ref="B239:B239" r:id="R011a19d645a349d3" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B240:B240" r:id="R26703f2e438246e6" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
-    <x:hyperlink ref="B241:B241" r:id="Rcd84dd56d1e147c9" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B242:B242" r:id="R93e6f93cde894323" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B243:B243" r:id="Rca97b442bb644bca" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B244:B244" r:id="R2986ac8ec96c49d0" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B245:B245" r:id="Rddcf2afa2686411e" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
-    <x:hyperlink ref="B246:B246" r:id="R7d005f84fc2e475f" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B247:B247" r:id="R59b7557741ce4143" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
-    <x:hyperlink ref="B248:B248" r:id="Rbfe1f024a7314553" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B249:B249" r:id="Rfa6350ed19324933" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B250:B250" r:id="Rf9a9a9f227b64093" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
-    <x:hyperlink ref="B251:B251" r:id="Rd6ed3a9b2e134a6c" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B252:B252" r:id="R22b0a96e41894b5e" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B253:B253" r:id="Rf5bd8be242d04b76" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B254:B254" r:id="R366319d1af714d0f" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B255:B255" r:id="R5d55f43bc4ee4ac7" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B256:B256" r:id="R080b9e4369b7413d" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
-    <x:hyperlink ref="B257:B257" r:id="R1846206d29e4403a" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
-    <x:hyperlink ref="B258:B258" r:id="R56fa2ce159e44eb8" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B259:B259" r:id="R98eae38991f24b8b" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B260:B260" r:id="Rdcc770c670284196" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
-    <x:hyperlink ref="B261:B261" r:id="Ra3a2283ad12d48ee" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B262:B262" r:id="R5db9f7a7b96c4d1f" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
-    <x:hyperlink ref="B263:B263" r:id="R92a71e0d71694efa" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
-    <x:hyperlink ref="B264:B264" r:id="R22097a3152144bae" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B265:B265" r:id="R728e2b69ffdf4409" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B266:B266" r:id="R5b951a31423043fb" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B267:B267" r:id="Rcf41fe6d38b94d20" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B268:B268" r:id="Rd12bfe23a0ca4277" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B269:B269" r:id="R7cca275932454c3b" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
-    <x:hyperlink ref="B270:B270" r:id="R2a8234996567409d" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B271:B271" r:id="Rf6beec0f024f484f" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
-    <x:hyperlink ref="B272:B272" r:id="R251f2906477b4cc2" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
-    <x:hyperlink ref="B273:B273" r:id="Rbcb09db47da74123" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B274:B274" r:id="Rb0db9618a93d426c" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B275:B275" r:id="R25c7047c33174312" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
-    <x:hyperlink ref="B276:B276" r:id="Rad147535aaf24d45" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
-    <x:hyperlink ref="B277:B277" r:id="R54c9b5c389634627" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B278:B278" r:id="R1fb9d6ad8ec94cd2" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B279:B279" r:id="R8b5bdcf4ca7647d7" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B280:B280" r:id="R4ea2856778cb41be" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
-    <x:hyperlink ref="B281:B281" r:id="R2b32f10ce3c44ad1" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B282:B282" r:id="R84cf3d96da834dcf" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B283:B283" r:id="R3d429849df774ab0" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
-    <x:hyperlink ref="B284:B284" r:id="R6a1989db4e614e27" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
-    <x:hyperlink ref="B285:B285" r:id="Ra356f9ac5cc24e58" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B286:B286" r:id="R8865b451480041ef" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B287:B287" r:id="Ra7133365f9c54d03" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
-    <x:hyperlink ref="B288:B288" r:id="R75c0730242a54a68" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
-    <x:hyperlink ref="B289:B289" r:id="Rbf1223eff5354e82" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B290:B290" r:id="R071355f934e34725" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
-    <x:hyperlink ref="B291:B291" r:id="Rc75460583d3b4c0b" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
-    <x:hyperlink ref="B292:B292" r:id="R748e3bb6a42d4eaf" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
-    <x:hyperlink ref="B293:B293" r:id="Rbacb36ea22d64c61" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
-    <x:hyperlink ref="B294:B294" r:id="Rd325bfddb3904d88" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B295:B295" r:id="R4b053248269441c7" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B296:B296" r:id="Rf8f7504a4ab04943" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
-    <x:hyperlink ref="B297:B297" r:id="R3d21ca378ccb49bd" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
-    <x:hyperlink ref="B298:B298" r:id="R3d6c143b14634e24" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B299:B299" r:id="R16898b23ca5f4f52" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B300:B300" r:id="R1fc611531d334a04" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B301:B301" r:id="Rde9519e745c54842" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B302:B302" r:id="R46ef2e77e68d4a0b" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B303:B303" r:id="R746104b3879a4bbb" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
-    <x:hyperlink ref="B304:B304" r:id="Rcf19faa6c2334c86" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B305:B305" r:id="R4ded5ee2b6214dbc" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B306:B306" r:id="R0b647a2476fc4151" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
-    <x:hyperlink ref="B307:B307" r:id="Rcd6ac00533224fc2" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
-    <x:hyperlink ref="B308:B308" r:id="R3db9e3670abe43c2" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B309:B309" r:id="Rf342b4bf4e8e405b" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B310:B310" r:id="R448b2c159eab4d8d" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
-    <x:hyperlink ref="B311:B311" r:id="R9f9b41d71fae46c6" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
-    <x:hyperlink ref="B312:B312" r:id="R0614a9fa0af2423d" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B313:B313" r:id="Rc4436eee38734b91" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B314:B314" r:id="Rdc276cf99ca24eab" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B315:B315" r:id="Rf307df2f7b2a4066" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
-    <x:hyperlink ref="B316:B316" r:id="R641e4cd2e6274508" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
-    <x:hyperlink ref="B317:B317" r:id="R01e0b83bd5d148a5" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
-    <x:hyperlink ref="B318:B318" r:id="R3047ed6d5e2340ec" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
-    <x:hyperlink ref="B319:B319" r:id="R8cd769e5de1b4fda" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B320:B320" r:id="R1096ab1023244d9d" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
-    <x:hyperlink ref="B321:B321" r:id="Rdf93a80bc19946ce" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B322:B322" r:id="R141b3ad4dfcd4b59" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
-    <x:hyperlink ref="B323:B323" r:id="R5d34c056d76b4090" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B324:B324" r:id="R19585aab27bf4b93" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B325:B325" r:id="R440a1436d5ea49bd" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
-    <x:hyperlink ref="B326:B326" r:id="R599c292a3c674f82" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B327:B327" r:id="R832aa5ee49ee47d6" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B328:B328" r:id="Rc195d51cd1a54ade" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
-    <x:hyperlink ref="B329:B329" r:id="Rf3a646a59b6d4f67" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B330:B330" r:id="R2dea5588b2fa4804" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
-    <x:hyperlink ref="B331:B331" r:id="R44affc83d8914e2a" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B332:B332" r:id="R9a76b2cfb8424a98" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
-    <x:hyperlink ref="B333:B333" r:id="Rbf761dfc36024f72" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B334:B334" r:id="Rc994257a33ab45a8" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
-    <x:hyperlink ref="B335:B335" r:id="R7fc5f3382f25401f" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
-    <x:hyperlink ref="B336:B336" r:id="Rf0992d85a19347ab" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B337:B337" r:id="R7e5d838f4ac04cae" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B338:B338" r:id="R0e5931284bcb4e61" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
-    <x:hyperlink ref="B339:B339" r:id="R5d854ea4806e4d21" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B340:B340" r:id="Re0bd68eb29874a7b" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B341:B341" r:id="R219f95b0e92b4721" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
-    <x:hyperlink ref="B342:B342" r:id="R3d7c8fb1c06845d1" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
-    <x:hyperlink ref="B343:B343" r:id="Rc2d8ebbf10fa40b0" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B344:B344" r:id="Rb0c1bbcb2c0c4422" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
-    <x:hyperlink ref="B345:B345" r:id="R3322fca9fd794062" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
-    <x:hyperlink ref="B346:B346" r:id="R728da9b750094e7a" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
-    <x:hyperlink ref="B347:B347" r:id="R09904bfa2df14656" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
-    <x:hyperlink ref="B348:B348" r:id="Re2c2750295c14a7c" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B349:B349" r:id="Radfd415056ee4034" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B350:B350" r:id="R7419805829e54429" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
-    <x:hyperlink ref="B351:B351" r:id="R636a264a32e74081" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
-    <x:hyperlink ref="B352:B352" r:id="R9b1fba3342eb49a7" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
-    <x:hyperlink ref="B353:B353" r:id="Rdde2947532944ca1" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
-    <x:hyperlink ref="B354:B354" r:id="Re57efb25ce4a4159" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B355:B355" r:id="Rfd8e4831be5344d1" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B356:B356" r:id="R51822c21cd544ed6" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B357:B357" r:id="R4f194c994f744ff3" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
-    <x:hyperlink ref="B358:B358" r:id="Rc764c5e7aa36469e" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
-    <x:hyperlink ref="B359:B359" r:id="Rba0b61ab6c0e4642" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
-    <x:hyperlink ref="B360:B360" r:id="Re6b6808eb3dc4f8d" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
-    <x:hyperlink ref="B361:B361" r:id="Rb99419e7f78e4736" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B362:B362" r:id="R2d0e820a2e45490e" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B363:B363" r:id="R9a5775c677654751" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B364:B364" r:id="R9a980f06bea649ff" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
-    <x:hyperlink ref="B365:B365" r:id="R278a669a73b24dd7" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
-    <x:hyperlink ref="B366:B366" r:id="R89e7cbf842684e45" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B367:B367" r:id="Rcb2e76d3a1de4b97" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B368:B368" r:id="Re1617e483c3542c6" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
-    <x:hyperlink ref="B369:B369" r:id="Rbc6080c223c24836" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
-    <x:hyperlink ref="B370:B370" r:id="Rc242366d06f1435c" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
-    <x:hyperlink ref="B371:B371" r:id="R8962c685e8ec4c25" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B372:B372" r:id="Rf0d3c50cfb834e29" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B373:B373" r:id="R413daee19dd44819" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B374:B374" r:id="Ree447bf4b8504ef2" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B375:B375" r:id="R15fe11a318dc49d7" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B376:B376" r:id="R3f5b4676a0b5423e" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
-    <x:hyperlink ref="B377:B377" r:id="Rd42b88ac1e454627" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B378:B378" r:id="Rd5d96a7eef434983" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B379:B379" r:id="R15416d14c50d48c3" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B380:B380" r:id="Rb0985b2bb4d84ca7" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B381:B381" r:id="R4e3e298a8d41453a" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B382:B382" r:id="Re1c620db5886426c" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
-    <x:hyperlink ref="B383:B383" r:id="Rc21ce8810c974f10" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B384:B384" r:id="Rdcfcf52cce4640d9" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
-    <x:hyperlink ref="B385:B385" r:id="Rf07c4b1246354a40" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B386:B386" r:id="Rbe65dec7150a466c" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B387:B387" r:id="R4a5e06d9ef1b4662" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B388:B388" r:id="R5e2bd8121d0d452e" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
-    <x:hyperlink ref="B389:B389" r:id="Rbacf8862d9e24f58" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B390:B390" r:id="R619d7b0f63734ae6" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
-    <x:hyperlink ref="B391:B391" r:id="R5d3c7ac0033a41ba" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B392:B392" r:id="R9c12c86a138143f2" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
-    <x:hyperlink ref="B393:B393" r:id="Raba44841302548f6" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
-    <x:hyperlink ref="B394:B394" r:id="R0d43a25057784e7a" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B395:B395" r:id="Ra5c53c1c852d464c" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B396:B396" r:id="Ra286b76f55f1496d" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B397:B397" r:id="R2f424c67c3bb41bd" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
-    <x:hyperlink ref="B398:B398" r:id="Rfc86f0b3fc1d4ff9" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B399:B399" r:id="R8ed35939e23d43cd" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B400:B400" r:id="R2ad4db2fd11d46ac" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B401:B401" r:id="Rfd45266cbfba49c1" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B402:B402" r:id="R0665a7443a0641e8" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
-    <x:hyperlink ref="B403:B403" r:id="Re80f963180ab4daf" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B404:B404" r:id="R610e108dc452477d" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
-    <x:hyperlink ref="B405:B405" r:id="R88c41e6d9d4a496f" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B406:B406" r:id="R7e18efe334484f34" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B407:B407" r:id="Rc7caec1334cf4ebb" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B408:B408" r:id="R57f0ab895b464368" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
-    <x:hyperlink ref="B409:B409" r:id="Rb1cd2557f51346d3" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B410:B410" r:id="R2378f41f49984307" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
-    <x:hyperlink ref="B411:B411" r:id="R9eece941920441fc" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
-    <x:hyperlink ref="B412:B412" r:id="R2205987ec4254c9d" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
-    <x:hyperlink ref="B413:B413" r:id="R6db297799e2e4a80" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B414:B414" r:id="R487aae73b6094ef9" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B415:B415" r:id="R52ff9c8405aa40ac" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
-    <x:hyperlink ref="B416:B416" r:id="Rdfa572bcab0f49ba" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B417:B417" r:id="Rdc5d7aae88d34284" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B418:B418" r:id="R39ebf6d08f9b4fde" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B419:B419" r:id="Rd781ecb496a64504" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
-    <x:hyperlink ref="B420:B420" r:id="R02a4f3aaa73748fa" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
-    <x:hyperlink ref="B421:B421" r:id="R8376088d3562420f" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
-    <x:hyperlink ref="B422:B422" r:id="R7999153050c149cc" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
-    <x:hyperlink ref="B423:B423" r:id="R5312134eb8084d88" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
-    <x:hyperlink ref="B424:B424" r:id="R31572fc1a0e3484d" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B425:B425" r:id="Rf1ae8fb1174a4e22" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B426:B426" r:id="R39626255a5f0446a" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B427:B427" r:id="R4f7762e300e541ba" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
-    <x:hyperlink ref="B428:B428" r:id="Rdaab7e3a44804f8e" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
-    <x:hyperlink ref="B429:B429" r:id="R79d7340726b646a1" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
-    <x:hyperlink ref="B430:B430" r:id="Rb22c65a33a444540" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B431:B431" r:id="Rc32fe4389d634c0b" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B432:B432" r:id="Re84d4772ce7f4cdd" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B433:B433" r:id="R935bb767c3674252" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B434:B434" r:id="R3f46ac4a2f1e40da" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B435:B435" r:id="Rffe53a336ef04281" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
-    <x:hyperlink ref="B436:B436" r:id="R5c81c47cab984378" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
-    <x:hyperlink ref="B437:B437" r:id="R507920d9c2d54456" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
-    <x:hyperlink ref="B438:B438" r:id="Rb856c83270e14e4a" display="https://etf.dws.com//en-gb/LU3313127113-eurozone-government-bond-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B439:B439" r:id="R5729e003b3ce4c7f" display="https://etf.dws.com//en-gb/LU3353962601-msci-world-swap-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B440:B440" r:id="Rbbc91e1fe8244902" display="https://etf.dws.com//en-gb/LU3353962783-s-p-500-swap-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B441:B441" r:id="Rc56491d0f3a24a56" display="https://etf.dws.com//en-gb/LU3353962866-stoxx-global-select-dividend-100-swap-ucits-etf-ic-usd-unlisted/"/>
-    <x:hyperlink ref="B442:B442" r:id="R2461d218ce4e4e6a" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
-    <x:hyperlink ref="B443:B443" r:id="Rc537e786ca474655" display="https://etf.dws.com//en-gb/LU3370249040-bloomberg-commodity-swap-ucits-etf-3c-gbp-hedged/"/>
-    <x:hyperlink ref="B444:B444" r:id="Rb70219e3a88b4ab0" display="https://etf.dws.com//en-gb/LU3375213041-msci-world-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B8:B8" r:id="R28cdaf9ba4ce4f1a" display="https://etf.dws.com//en-gb/IE00002ZKAP0-europe-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B9:B9" r:id="R8ddac3771dc64a41" display="https://etf.dws.com//en-gb/IE00004DJ199-msci-world-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B10:B10" r:id="R6ce52e9b92d146c2" display="https://etf.dws.com//en-gb/IE0000K7HU41-msci-usa-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B11:B11" r:id="Rb2849221625549b0" display="https://etf.dws.com//en-gb/IE0000MMQ5M5-msci-usa-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B12:B12" r:id="R59661f0b1085421e" display="https://etf.dws.com//en-gb/IE0001JH5CB4-europe-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B13:B13" r:id="R93349c0d1ffe41d8" display="https://etf.dws.com//en-gb/IE0001TLQX55-s-p-500-garp-ucits-etf-1c/"/>
+    <x:hyperlink ref="B14:B14" r:id="R05bb50466bfb48c5" display="https://etf.dws.com//en-gb/IE00028H9QJ8-usd-corporate-green-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B15:B15" r:id="R09c81b40391b432d" display="https://etf.dws.com//en-gb/IE0002EI5AG0-s-p-500-equal-weight-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B16:B16" r:id="Rc1a09d676404437d" display="https://etf.dws.com//en-gb/IE0002GFATQ6-s-p-500-equal-weight-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B17:B17" r:id="R6d827fd6c9754595" display="https://etf.dws.com//en-gb/IE0002PGSLZ5-us-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B18:B18" r:id="R71df072a83354cb1" display="https://etf.dws.com//en-gb/IE0002ZM3JI1-usa-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B19:B19" r:id="Raf61e87331344b8d" display="https://etf.dws.com//en-gb/IE00036F4K40-msci-global-sdg-3-good-health-ucits-etf-1c/"/>
+    <x:hyperlink ref="B20:B20" r:id="Rb1e762e31dac4f18" display="https://etf.dws.com//en-gb/IE0003NQ0IY5-msci-world-quality-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B21:B21" r:id="R76b1a49ab6b54cfa" display="https://etf.dws.com//en-gb/IE0003W9O921-usd-corporate-green-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B22:B22" r:id="Rb8479dbd73854bbe" display="https://etf.dws.com//en-gb/IE000472H9T4-nasdaq-100-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B23:B23" r:id="R691cc55ac9aa4771" display="https://etf.dws.com//en-gb/IE0004KLW911-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1c/"/>
+    <x:hyperlink ref="B24:B24" r:id="Rf6370929011b41c3" display="https://etf.dws.com//en-gb/IE0004MFRED4-s-p-500-equal-weight-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B25:B25" r:id="R8b092dbb1ad64a0e" display="https://etf.dws.com//en-gb/IE0004ZJGWT9-msci-europe-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B26:B26" r:id="Rf38630969d5b46b4" display="https://etf.dws.com//en-gb/IE0005E47AH7-msci-global-sdg-9-industry-innovation-infrastructure-ucits-etf-1c/"/>
+    <x:hyperlink ref="B27:B27" r:id="R0845a9cbcc2c4be4" display="https://etf.dws.com//en-gb/IE0006FDYJF8-msci-japan-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B28:B28" r:id="R48040df2607e4ea2" display="https://etf.dws.com//en-gb/IE0006FFX5U1-msci-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B29:B29" r:id="Rdb7b8ca68b1e4edc" display="https://etf.dws.com//en-gb/IE0006GNB732-eur-high-yield-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B30:B30" r:id="Rd394a4cf8b0e4a49" display="https://etf.dws.com//en-gb/IE0006I3NZF8-msci-usa-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B31:B31" r:id="R036a123bc3c848f4" display="https://etf.dws.com//en-gb/IE0006WW1TQ4-msci-world-ex-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B32:B32" r:id="Re1eb0ebf086d4edf" display="https://etf.dws.com//en-gb/IE0006YM7D84-usd-high-yield-corporate-bond-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B33:B33" r:id="Rc93b3621d498442a" display="https://etf.dws.com//en-gb/IE00074JLU02-japan-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B34:B34" r:id="Re5f91d2f80a049a5" display="https://etf.dws.com//en-gb/IE0007ULOZS8-s-p-500-scored-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B35:B35" r:id="R7fde7cb998084784" display="https://etf.dws.com//en-gb/IE0007WJ6B10-msci-global-clean-water-sanitation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B36:B36" r:id="Rcc37713615d94cd6" display="https://etf.dws.com//en-gb/IE0008YN0OY8-msci-world-minimum-volatility-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B37:B37" r:id="Re36b474e37224f98" display="https://etf.dws.com//en-gb/IE00094GSCQ4-world-equity-enhanced-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B38:B38" r:id="Rb82f93c222554205" display="https://etf.dws.com//en-gb/IE0009KLWT21-msci-world-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B39:B39" r:id="Re2dfd26d1f9944d7" display="https://etf.dws.com//en-gb/IE000BO2Y0T8-msci-nordic-ucits-etf-1c/"/>
+    <x:hyperlink ref="B40:B40" r:id="R5396c94a953c463e" display="https://etf.dws.com//en-gb/IE000CXLGK86-s-p-500-equal-weight-ucits-etf-2d/"/>
+    <x:hyperlink ref="B41:B41" r:id="R3168795957d443be" display="https://etf.dws.com//en-gb/IE000DNSAS54-msci-emerging-markets-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B42:B42" r:id="R37975f1fd16b478a" display="https://etf.dws.com//en-gb/IE000DVHJV46-s-p-500-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B43:B43" r:id="R9125b70e39964b27" display="https://etf.dws.com//en-gb/IE000E0V65D8-world-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B44:B44" r:id="R1c563e5c6fe0428b" display="https://etf.dws.com//en-gb/IE000E4BATC9-msci-world-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B45:B45" r:id="R7c1d714b09794349" display="https://etf.dws.com//en-gb/IE000ER61U30-msci-europe-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B46:B46" r:id="R3ff6966868bd4efd" display="https://etf.dws.com//en-gb/IE000EVOVOG1-msci-usa-positioning-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B47:B47" r:id="Rb54aa5229fe7478d" display="https://etf.dws.com//en-gb/IE000EXUE0G2-nasdaq-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B48:B48" r:id="R245a5cba0b3a4317" display="https://etf.dws.com//en-gb/IE000F04HGE5-floating-rate-notes-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B49:B49" r:id="Rf4e1ae7aaf174492" display="https://etf.dws.com//en-gb/IE000F354Q61-msci-world-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B50:B50" r:id="R6c6fc8be3cc64dd9" display="https://etf.dws.com//en-gb/IE000FL46JJ1-s-p-500-equal-weight-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B51:B51" r:id="R3881556298cf4274" display="https://etf.dws.com//en-gb/IE000FO05UG4-s-p-500-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B52:B52" r:id="R2a3e9c5f921f4cfd" display="https://etf.dws.com//en-gb/IE000FO1A5D1-s-p-500-equal-weight-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B53:B53" r:id="Rdbc00925040c4099" display="https://etf.dws.com//en-gb/IE000FW16TX1-msci-usa-swap-ii-ucits-etf-1d/"/>
+    <x:hyperlink ref="B54:B54" r:id="R900e8b6925724056" display="https://etf.dws.com//en-gb/IE000GF6QTP6-s-p-500-equal-weight-scored-screened-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B55:B55" r:id="R48ddb3ffac6b42a8" display="https://etf.dws.com//en-gb/IE000GWA2J58-msci-emerging-markets-ucits-etf-1d/"/>
+    <x:hyperlink ref="B56:B56" r:id="R8d756c6cfa07478f" display="https://etf.dws.com//en-gb/IE000GYDNJS5-msci-usa-climate-transition-ucits-etf-1d/"/>
+    <x:hyperlink ref="B57:B57" r:id="Re5e38a9f415a480c" display="https://etf.dws.com//en-gb/IE000HT7E0B1-nordic-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B58:B58" r:id="Rbf3b246b2f674ae0" display="https://etf.dws.com//en-gb/IE000HY30YW6-s-p-500-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B59:B59" r:id="R2cd23624e13445e4" display="https://etf.dws.com//en-gb/IE000IDLWOL4-s-p-500-equal-weight-scored-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B60:B60" r:id="R1faf79b79df04afc" display="https://etf.dws.com//en-gb/IE000INYW0A7-msci-world-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B61:B61" r:id="Ra63026e4b3fc4372" display="https://etf.dws.com//en-gb/IE000ISS8DB2-msci-world-small-cap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B62:B62" r:id="R4dd3259fb93f4a1c" display="https://etf.dws.com//en-gb/IE000JZYIUN0-msci-global-sdg-7-affordable-and-clean-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B63:B63" r:id="R4e4d698ebbe7413c" display="https://etf.dws.com//en-gb/IE000KD0BZ68-msci-genomic-healthcare-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B64:B64" r:id="Rec1329c187bf4f99" display="https://etf.dws.com//en-gb/IE000L2IS494-msci-global-social-fairness-contributors-ucits-etf-1c/"/>
+    <x:hyperlink ref="B65:B65" r:id="Re21111bcd9af434b" display="https://etf.dws.com//en-gb/IE000L6ZMMC4-ftse-all-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B66:B66" r:id="R67712576cb804bc8" display="https://etf.dws.com//en-gb/IE000LAUZQT6-msci-world-value-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B67:B67" r:id="R3adfa0cfa7ac459d" display="https://etf.dws.com//en-gb/IE000LOSV2D0-usa-biodiversity-focus-sri-ucits-etf-1c/"/>
+    <x:hyperlink ref="B68:B68" r:id="Ra9b2978d55b847f9" display="https://etf.dws.com//en-gb/IE000M8F3JA6-global-growth-leaders-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B69:B69" r:id="R36619b01560440d4" display="https://etf.dws.com//en-gb/IE000MCVFK47-eur-corporate-green-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B70:B70" r:id="R83cd9183f4074f9d" display="https://etf.dws.com//en-gb/IE000ME8PWJ4-msci-world-utilities-ucits-etf-1d/"/>
+    <x:hyperlink ref="B71:B71" r:id="Re9743c10f82148c2" display="https://etf.dws.com//en-gb/IE000MF9SZ46-msci-nordic-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B72:B72" r:id="R2228464df0f24608" display="https://etf.dws.com//en-gb/IE000N5GJDD7-s-p-500-equal-weight-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B73:B73" r:id="R3adc1f4643bd458f" display="https://etf.dws.com//en-gb/IE000N9MLVT1-msci-europe-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B74:B74" r:id="R94fb89fceef64f6c" display="https://etf.dws.com//en-gb/IE000NS5HRY9-msci-world-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B75:B75" r:id="Rcff9ec6058a24c5c" display="https://etf.dws.com//en-gb/IE000O7Q2E56-electrification-technologies-smart-grid-ucits-etf-1c/"/>
+    <x:hyperlink ref="B76:B76" r:id="Ra229dd705f844278" display="https://etf.dws.com//en-gb/IE000ONQ3X90-msci-world-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B77:B77" r:id="Re81cea5f7b794157" display="https://etf.dws.com//en-gb/IE000P4AYI47-msci-world-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B78:B78" r:id="R9ca837581f434ba2" display="https://etf.dws.com//en-gb/IE000PDUVTF3-msci-usa-swap-ii-ucits-etf-1c/"/>
+    <x:hyperlink ref="B79:B79" r:id="R174ea80148ee4990" display="https://etf.dws.com//en-gb/IE000PSF3A70-msci-global-sdgs-ucits-etf-1c/"/>
+    <x:hyperlink ref="B80:B80" r:id="R1606766b7b1f4ab9" display="https://etf.dws.com//en-gb/IE000QVYFUT7-india-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B81:B81" r:id="R38c7d83591164ac9" display="https://etf.dws.com//en-gb/IE000RNHIKK1-msci-usa-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B82:B82" r:id="Ra4cd983095e64ee8" display="https://etf.dws.com//en-gb/IE000SRQBBT6-s-p-500-defensive-shareholder-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B83:B83" r:id="R6bb449e312124ca6" display="https://etf.dws.com//en-gb/IE000SZ25OI0-s-p-500-equal-weight-scored-screened-ucits-etf-4c-gbp-hedged/"/>
+    <x:hyperlink ref="B84:B84" r:id="R4cbafe19aa1048f9" display="https://etf.dws.com//en-gb/IE000TL3PL69-msci-world-momentum-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B85:B85" r:id="R3affbc6affb44ae5" display="https://etf.dws.com//en-gb/IE000TSML5I8-msci-usa-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B86:B86" r:id="R365be1f6ffd14ff3" display="https://etf.dws.com//en-gb/IE000TZT8TI0-emerging-markets-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B87:B87" r:id="R57696ca7da1b4024" display="https://etf.dws.com//en-gb/IE000UATQPE2-msci-world-small-cap-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B88:B88" r:id="Rfedad44ff4344bcb" display="https://etf.dws.com//en-gb/IE000UMV0L21-msci-usa-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B89:B89" r:id="R80800e3e7a4d48ae" display="https://etf.dws.com//en-gb/IE000UP2BIZ9-s-p-500-ucits-etf-4d/"/>
+    <x:hyperlink ref="B90:B90" r:id="R8d0822a3898144af" display="https://etf.dws.com//en-gb/IE000UX5WPU4-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B91:B91" r:id="R87090c5080ee47b9" display="https://etf.dws.com//en-gb/IE000UZCJS58-world-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B92:B92" r:id="Rbd3565f97c93488d" display="https://etf.dws.com//en-gb/IE000V04SL39-msci-usa-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B93:B93" r:id="R583e3dddfb554371" display="https://etf.dws.com//en-gb/IE000V0GDVU7-msci-global-sdg-11-sustainable-cities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B94:B94" r:id="R51f5673a9e8f46d0" display="https://etf.dws.com//en-gb/IE000VCBWFL8-msci-emu-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B95:B95" r:id="R7b93ec0bfb304f6f" display="https://etf.dws.com//en-gb/IE000VCTBRW6-msci-world-industrials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B96:B96" r:id="Ra66ff51c4456468e" display="https://etf.dws.com//en-gb/IE000VXC51U5-msci-ac-world-screened-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B97:B97" r:id="Re8787eb56fe349b9" display="https://etf.dws.com//en-gb/IE000W6L2AI3-msci-emu-climate-transition-ucits-etf-1c/"/>
+    <x:hyperlink ref="B98:B98" r:id="Ra0784b93fd214156" display="https://etf.dws.com//en-gb/IE000WGF1X01-msci-ac-world-screened-ucits-etf-5c-usd-hedged/"/>
+    <x:hyperlink ref="B99:B99" r:id="Rf1b5f36955f4427a" display="https://etf.dws.com//en-gb/IE000WHO5BF2-usd-high-yield-corporate-bond-screened-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B100:B100" r:id="Re824066859f54e19" display="https://etf.dws.com//en-gb/IE000WQ16XQ4-msci-europe-high-dividend-yield-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B101:B101" r:id="R7194de8944184348" display="https://etf.dws.com//en-gb/IE000X1GW0A7-msci-world-imi-ucits-etf-1c/"/>
+    <x:hyperlink ref="B102:B102" r:id="R262bb87bf02a43e1" display="https://etf.dws.com//en-gb/IE000X4A4GV2-global-equity-top-active-ucits-etf-1c/"/>
+    <x:hyperlink ref="B103:B103" r:id="R6bf305d1d87d40ef" display="https://etf.dws.com//en-gb/IE000X5MRP46-msci-usa-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B104:B104" r:id="R13e93dfb883e4c4a" display="https://etf.dws.com//en-gb/IE000X63FXN4-usd-corporate-green-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B105:B105" r:id="Rb321b7d68d93424c" display="https://etf.dws.com//en-gb/IE000X6Z71P5-msci-usa-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B106:B106" r:id="Rc3879aee44824f73" display="https://etf.dws.com//en-gb/IE000XOQ9TK4-msci-next-generation-internet-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B107:B107" r:id="R498c2e391f1d4aec" display="https://etf.dws.com//en-gb/IE000Y6L6LE6-emu-net-zero-pathway-paris-aligned-ucits-etf-1c/"/>
+    <x:hyperlink ref="B108:B108" r:id="R598356a212bc4a23" display="https://etf.dws.com//en-gb/IE000Y6ZXZ48-msci-global-circular-economy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B109:B109" r:id="Re27ede8066b64099" display="https://etf.dws.com//en-gb/IE000YDOORK7-msci-fintech-innovation-ucits-etf-1c/"/>
+    <x:hyperlink ref="B110:B110" r:id="R7584f8c0615441f7" display="https://etf.dws.com//en-gb/IE000YKHGYN2-ftse-all-world-ex-us-ucits-etf-1c/"/>
+    <x:hyperlink ref="B111:B111" r:id="R91a949b407af4799" display="https://etf.dws.com//en-gb/IE000Z0FC0G5-msci-world-ex-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B112:B112" r:id="R6c3e6b04e87e4ba3" display="https://etf.dws.com//en-gb/IE000Z9SJA06-s-p-500-ucits-etf-4c/"/>
+    <x:hyperlink ref="B113:B113" r:id="Rffbc7a03ff51490e" display="https://etf.dws.com//en-gb/IE00B3Y8D011-portfolio-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B114:B114" r:id="Rd4396328e98b4e25" display="https://etf.dws.com//en-gb/IE00B8KMSQ34-s-p-500-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B115:B115" r:id="Rd6649002137b4543" display="https://etf.dws.com//en-gb/IE00B9MRHC27-msci-nordic-ucits-etf-1d/"/>
+    <x:hyperlink ref="B116:B116" r:id="R0ded33201449451b" display="https://etf.dws.com//en-gb/IE00B9MRJJ36-mdax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B117:B117" r:id="R03ddf20c726945e4" display="https://etf.dws.com//en-gb/IE00BCHWNQ94-msci-world-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B118:B118" r:id="Rce52acb3c7e1469d" display="https://etf.dws.com//en-gb/IE00BCHWNS19-msci-usa-energy-ucits-etf-1d/"/>
+    <x:hyperlink ref="B119:B119" r:id="R0805a72da2c44f94" display="https://etf.dws.com//en-gb/IE00BCHWNT26-msci-usa-financials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B120:B120" r:id="R92acd27e451c4dfc" display="https://etf.dws.com//en-gb/IE00BCHWNV48-msci-usa-industrials-ucits-etf-1d/"/>
+    <x:hyperlink ref="B121:B121" r:id="R3a8f3dc7250c4c4c" display="https://etf.dws.com//en-gb/IE00BCHWNW54-msci-usa-health-care-ucits-etf-1d/"/>
+    <x:hyperlink ref="B122:B122" r:id="Rb69264296f70439b" display="https://etf.dws.com//en-gb/IE00BD4DX952-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B123:B123" r:id="R8d9b1c8f9a974e18" display="https://etf.dws.com//en-gb/IE00BD4DXB77-esg-usd-emerging-markets-bond-quality-weighted-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B124:B124" r:id="R360ad1e616ba4c74" display="https://etf.dws.com//en-gb/IE00BDB7J586-msci-usa-minimum-volatility-ucits-etf-1d/"/>
+    <x:hyperlink ref="B125:B125" r:id="R988737c78da5486c" display="https://etf.dws.com//en-gb/IE00BDGN9Z19-msci-emu-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B126:B126" r:id="R8599000abae846c9" display="https://etf.dws.com//en-gb/IE00BDR5HM97-usd-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B127:B127" r:id="R2adf4bc29db94c5a" display="https://etf.dws.com//en-gb/IE00BDR5HN05-usd-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B128:B128" r:id="Rc436705eaa1146d7" display="https://etf.dws.com//en-gb/IE00BDVPTJ63-msci-usa-banks-ucits-etf-1d/"/>
+    <x:hyperlink ref="B129:B129" r:id="R12ea2ab695774eee" display="https://etf.dws.com//en-gb/IE00BF8J5974-usd-corporate-bond-short-duration-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B130:B130" r:id="R0fe930c1bfd343d8" display="https://etf.dws.com//en-gb/IE00BFMKQ930-usd-corporate-bond-short-duration-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B131:B131" r:id="R0d580f27c36d4613" display="https://etf.dws.com//en-gb/IE00BFMKQC67-usd-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B132:B132" r:id="Re40b022069d44ae6" display="https://etf.dws.com//en-gb/IE00BFMNHK08-msci-europe-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B133:B133" r:id="R497347e9f5d74434" display="https://etf.dws.com//en-gb/IE00BFMNPS42-msci-usa-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B134:B134" r:id="Rbf1f321c99d64628" display="https://etf.dws.com//en-gb/IE00BG04LT92-usd-high-yield-corporate-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B135:B135" r:id="R62c6d2399e9a45af" display="https://etf.dws.com//en-gb/IE00BG04LV15-usd-high-yield-corporate-bond-ucits-etf-4d-gbp-hedged/"/>
+    <x:hyperlink ref="B136:B136" r:id="R944e1144d3e24f29" display="https://etf.dws.com//en-gb/IE00BG04LY46-usd-corporate-bond-ucits-etf-5d-gbp-hedged/"/>
+    <x:hyperlink ref="B137:B137" r:id="Rac7b27b4b306456a" display="https://etf.dws.com//en-gb/IE00BG04LZ52-msci-usa-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B138:B138" r:id="Rf9ac75ea6d924480" display="https://etf.dws.com//en-gb/IE00BG04M077-msci-usa-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B139:B139" r:id="Rb484c6cd566c4ca8" display="https://etf.dws.com//en-gb/IE00BG36TC12-msci-japan-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B140:B140" r:id="R6a5b2cf840ee469b" display="https://etf.dws.com//en-gb/IE00BG370F43-msci-emerging-markets-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B141:B141" r:id="R3448c30c3962442b" display="https://etf.dws.com//en-gb/IE00BGHQ0G80-msci-ac-world-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B142:B142" r:id="Rf96d746486264a20" display="https://etf.dws.com//en-gb/IE00BGJWX091-s-p-500-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B143:B143" r:id="R302a58fc54f649f9" display="https://etf.dws.com//en-gb/IE00BGQYRQ28-msci-usa-consumer-staples-ucits-etf-1d/"/>
+    <x:hyperlink ref="B144:B144" r:id="Rc2be2cba1d0f4fd5" display="https://etf.dws.com//en-gb/IE00BGQYRR35-msci-usa-consumer-discretionary-ucits-etf-1d/"/>
+    <x:hyperlink ref="B145:B145" r:id="R09e258e327634408" display="https://etf.dws.com//en-gb/IE00BGQYRS42-msci-usa-information-technology-ucits-etf-1d/"/>
+    <x:hyperlink ref="B146:B146" r:id="Ra0336c7b30984a07" display="https://etf.dws.com//en-gb/IE00BGV5VM45-s-p-europe-ex-uk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B147:B147" r:id="R02a28445ade943ae" display="https://etf.dws.com//en-gb/IE00BGV5VN51-artificial-intelligence-big-data-ucits-etf-1c/"/>
+    <x:hyperlink ref="B148:B148" r:id="R32cc0ee9b5374731" display="https://etf.dws.com//en-gb/IE00BGV5VR99-future-mobility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B149:B149" r:id="Rb11f5750df1f4ae5" display="https://etf.dws.com//en-gb/IE00BH361H73-msci-north-america-high-dividend-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B150:B150" r:id="Reb0327d18ba041ab" display="https://etf.dws.com//en-gb/IE00BJ0KDQ92-msci-world-ucits-etf-1c/"/>
+    <x:hyperlink ref="B151:B151" r:id="R6263cfd06d3d4e20" display="https://etf.dws.com//en-gb/IE00BJ0KDR00-msci-usa-ucits-etf-1c/"/>
+    <x:hyperlink ref="B152:B152" r:id="R01517617cf534932" display="https://etf.dws.com//en-gb/IE00BJZ2DC62-msci-usa-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B153:B153" r:id="Re542097ace864cba" display="https://etf.dws.com//en-gb/IE00BJZ2DD79-russell-2000-ucits-etf-1c/"/>
+    <x:hyperlink ref="B154:B154" r:id="R1d260079e42f496f" display="https://etf.dws.com//en-gb/IE00BK1PV445-msci-usa-ucits-etf-1d/"/>
+    <x:hyperlink ref="B155:B155" r:id="Ra59072d2a2b4438b" display="https://etf.dws.com//en-gb/IE00BK1PV551-msci-world-ucits-etf-1d/"/>
+    <x:hyperlink ref="B156:B156" r:id="Rbcefb4fbc62949f9" display="https://etf.dws.com//en-gb/IE00BL25JL35-msci-world-quality-ucits-etf-1c/"/>
+    <x:hyperlink ref="B157:B157" r:id="R3d43e05f935246bf" display="https://etf.dws.com//en-gb/IE00BL25JM42-msci-world-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B158:B158" r:id="R6f45f2d72ad348b2" display="https://etf.dws.com//en-gb/IE00BL25JN58-msci-world-minimum-volatility-ucits-etf-1c/"/>
+    <x:hyperlink ref="B159:B159" r:id="R28ec473d12bd42d8" display="https://etf.dws.com//en-gb/IE00BL25JP72-msci-world-momentum-ucits-etf-1c/"/>
+    <x:hyperlink ref="B160:B160" r:id="Rbc7b7f4cf7ea42c6" display="https://etf.dws.com//en-gb/IE00BL58LJ19-usd-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B161:B161" r:id="R916f37df35c34f27" display="https://etf.dws.com//en-gb/IE00BL58LL31-usd-corporate-bond-sri-pab-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B162:B162" r:id="R491e68d94fed4f4d" display="https://etf.dws.com//en-gb/IE00BLNMYC90-s-p-500-equal-weight-ucits-etf-1c/"/>
+    <x:hyperlink ref="B163:B163" r:id="Rb21b79278687424a" display="https://etf.dws.com//en-gb/IE00BM67HJ62-msci-emerging-markets-ex-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B164:B164" r:id="R7c2000c562954caf" display="https://etf.dws.com//en-gb/IE00BM67HK77-msci-world-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B165:B165" r:id="Rd32cd33f24924b60" display="https://etf.dws.com//en-gb/IE00BM67HL84-msci-world-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B166:B166" r:id="R45814335674744b4" display="https://etf.dws.com//en-gb/IE00BM67HM91-msci-world-energy-ucits-etf-1c/"/>
+    <x:hyperlink ref="B167:B167" r:id="R771a687bd4b9480c" display="https://etf.dws.com//en-gb/IE00BM67HN09-msci-world-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B168:B168" r:id="Rd1bd1024e02f47c2" display="https://etf.dws.com//en-gb/IE00BM67HP23-msci-world-consumer-discretionary-ucits-etf-1c/"/>
+    <x:hyperlink ref="B169:B169" r:id="Rf74ca56f2f3f4b2c" display="https://etf.dws.com//en-gb/IE00BM67HQ30-msci-world-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B170:B170" r:id="Rf1d52711dc5f4131" display="https://etf.dws.com//en-gb/IE00BM67HR47-msci-world-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B171:B171" r:id="Rb8fd2e23692545dc" display="https://etf.dws.com//en-gb/IE00BM67HS53-msci-world-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B172:B172" r:id="R6539c4a5caa34e17" display="https://etf.dws.com//en-gb/IE00BM67HT60-msci-world-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B173:B173" r:id="Re8a337b1b61e4118" display="https://etf.dws.com//en-gb/IE00BM67HV82-msci-world-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B174:B174" r:id="R12728a0248554328" display="https://etf.dws.com//en-gb/IE00BM67HW99-s-p-500-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B175:B175" r:id="R996e7fe2d63a46b2" display="https://etf.dws.com//en-gb/IE00BM67HX07-s-p-500-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B176:B176" r:id="Rdb6e1d6a37d44bae" display="https://etf.dws.com//en-gb/IE00BM97MR69-us-treasuries-ultrashort-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B177:B177" r:id="Rb65d9889b2c34a88" display="https://etf.dws.com//en-gb/IE00BM97MV06-us-treasuries-ultrashort-bond-ucits-etf-3c-mxn-hedged/"/>
+    <x:hyperlink ref="B178:B178" r:id="R1b3b1b072e71453f" display="https://etf.dws.com//en-gb/IE00BMCFJ320-usd-corporate-bond-ucits-etf-6c-mxn-hedged/"/>
+    <x:hyperlink ref="B179:B179" r:id="R7cf97028e3a74b5f" display="https://etf.dws.com//en-gb/IE00BMFKG444-nasdaq-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B180:B180" r:id="R55027645c78b44c3" display="https://etf.dws.com//en-gb/IE00BMY76136-msci-world-esg-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B181:B181" r:id="R6f5eae7c26e340f6" display="https://etf.dws.com//en-gb/IE00BN2BCY94-developed-green-real-estate-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B182:B182" r:id="R098af99ad0334598" display="https://etf.dws.com//en-gb/IE00BNC1G699-msci-emu-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B183:B183" r:id="R125c96bcfc914d78" display="https://etf.dws.com//en-gb/IE00BNC1G707-msci-usa-communication-services-ucits-etf-1d/"/>
+    <x:hyperlink ref="B184:B184" r:id="R937530a137c6466d" display="https://etf.dws.com//en-gb/IE00BNKF6C99-stoxx-european-market-leaders-ucits-etf-1c/"/>
+    <x:hyperlink ref="B185:B185" r:id="R40dabcddd6424a4f" display="https://etf.dws.com//en-gb/IE00BP8FKB21-ftse-developed-europe-ex-uk-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B186:B186" r:id="R080f421dab964312" display="https://etf.dws.com//en-gb/IE00BPVLQD13-msci-japan-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B187:B187" r:id="R4e1889b73d4649b1" display="https://etf.dws.com//en-gb/IE00BPVLQF37-msci-japan-screened-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B188:B188" r:id="R2fb9e3f874ae4d95" display="https://etf.dws.com//en-gb/IE00BQXKVQ19-msci-gcc-select-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B189:B189" r:id="R9d1401fb1e484376" display="https://etf.dws.com//en-gb/IE00BRB36B93-msci-japan-screened-ucits-etf-3c-eur-hedged/"/>
+    <x:hyperlink ref="B190:B190" r:id="Rb2e6cc20af65467a" display="https://etf.dws.com//en-gb/IE00BTGD1B38-msci-japan-screened-ucits-etf-4c-usd-hedged/"/>
+    <x:hyperlink ref="B191:B191" r:id="R7fca96dfe5d24cca" display="https://etf.dws.com//en-gb/IE00BTJRMP35-msci-emerging-markets-ucits-etf-1c/"/>
+    <x:hyperlink ref="B192:B192" r:id="R9d8c87ae0a7544fb" display="https://etf.dws.com//en-gb/IE00BYPHT736-iboxx-eur-corporate-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B193:B193" r:id="R15b709db7ae1499c" display="https://etf.dws.com//en-gb/IE00BYZNF849-global-infrastructure-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B194:B194" r:id="R8bd4df28ec534227" display="https://etf.dws.com//en-gb/IE00BZ02LR44-msci-world-esg-ucits-etf-1c/"/>
+    <x:hyperlink ref="B195:B195" r:id="R6aecbbe403e54c33" display="https://etf.dws.com//en-gb/IE00BZ036H21-usd-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B196:B196" r:id="R35276c189a4042b2" display="https://etf.dws.com//en-gb/IE00BZ036J45-usd-corporate-bond-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B197:B197" r:id="R1dc6597918044453" display="https://etf.dws.com//en-gb/IE00BZ1BS790-msci-world-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B198:B198" r:id="Rb659938d8df64f18" display="https://etf.dws.com//en-gb/LU0274208692-msci-world-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B199:B199" r:id="R445b88ee8be843df" display="https://etf.dws.com//en-gb/LU0274209237-msci-europe-ucits-etf-1c/"/>
+    <x:hyperlink ref="B200:B200" r:id="R76be65baf21849c8" display="https://etf.dws.com//en-gb/LU0274209740-msci-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B201:B201" r:id="R0ba42a1b593040d4" display="https://etf.dws.com//en-gb/LU0274210672-msci-usa-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B202:B202" r:id="R079d9da3c27d48bc" display="https://etf.dws.com//en-gb/LU0274211217-euro-stoxx-50-ucits-etf-1d/"/>
+    <x:hyperlink ref="B203:B203" r:id="R36a0c7545a2d49f4" display="https://etf.dws.com//en-gb/LU0274211480-dax-ucits-etf-1c/"/>
+    <x:hyperlink ref="B204:B204" r:id="R7f4cc9819a0040b4" display="https://etf.dws.com//en-gb/LU0274212538-ftse-mib-ucits-etf-1d/"/>
+    <x:hyperlink ref="B205:B205" r:id="R7ece8591ae84443c" display="https://etf.dws.com//en-gb/LU0274221281-switzerland-ucits-etf-1d/"/>
+    <x:hyperlink ref="B206:B206" r:id="R437ba908e9544ec6" display="https://etf.dws.com//en-gb/LU0290355717-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B207:B207" r:id="Rcae6a54cf1864e36" display="https://etf.dws.com//en-gb/LU0290356871-eurozone-government-bond-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B208:B208" r:id="Rc23dabdcf8074061" display="https://etf.dws.com//en-gb/LU0290356954-eurozone-government-bond-3-5-ucits-etf-1c/"/>
+    <x:hyperlink ref="B209:B209" r:id="Rf9f0342333b944bc" display="https://etf.dws.com//en-gb/LU0290357176-eurozone-government-bond-5-7-ucits-etf-1c/"/>
+    <x:hyperlink ref="B210:B210" r:id="R92121d9165af4ea3" display="https://etf.dws.com//en-gb/LU0290357259-eurozone-government-bond-7-10-ucits-etf-1c/"/>
+    <x:hyperlink ref="B211:B211" r:id="Ra6e6ffeaec2f4999" display="https://etf.dws.com//en-gb/LU0290357507-eurozone-government-bond-15-30-ucits-etf-1c/"/>
+    <x:hyperlink ref="B212:B212" r:id="Rdf8247519a9d45cc" display="https://etf.dws.com//en-gb/LU0290357846-eurozone-government-bond-25-ucits-etf-1c/"/>
+    <x:hyperlink ref="B213:B213" r:id="R91927431ae164e94" display="https://etf.dws.com//en-gb/LU0290357929-global-inflation-linked-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B214:B214" r:id="R65ce7fed0c5a4891" display="https://etf.dws.com//en-gb/LU0290358224-eurozone-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B215:B215" r:id="R6822b50a2d954109" display="https://etf.dws.com//en-gb/LU0290358497-eur-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B216:B216" r:id="R635b6027445b4a76" display="https://etf.dws.com//en-gb/LU0292095535-euro-stoxx-quality-dividend-ucits-etf-1d/"/>
+    <x:hyperlink ref="B217:B217" r:id="Re2b68f460ca847da" display="https://etf.dws.com//en-gb/LU0292096186-stoxx-global-select-dividend-100-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B218:B218" r:id="Re2edb0a3c1384b41" display="https://etf.dws.com//en-gb/LU0292097234-ftse-100-income-ucits-etf-1d/"/>
+    <x:hyperlink ref="B219:B219" r:id="R0bf2723b63b04b76" display="https://etf.dws.com//en-gb/LU0292097317-ftse-250-ucits-etf-1d/"/>
+    <x:hyperlink ref="B220:B220" r:id="R9ba3844eb65e4e7a" display="https://etf.dws.com//en-gb/LU0292097747-msci-uk-esg-ucits-etf-1d/"/>
+    <x:hyperlink ref="B221:B221" r:id="R4b03cc75096f439b" display="https://etf.dws.com//en-gb/LU0292100046-msci-korea-ucits-etf-1c/"/>
+    <x:hyperlink ref="B222:B222" r:id="Ra0f0529fc0a3437b" display="https://etf.dws.com//en-gb/LU0292100806-msci-europe-materials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B223:B223" r:id="R743f533c3fb3462d" display="https://etf.dws.com//en-gb/LU0292103222-msci-europe-health-care-ucits-etf-1c/"/>
+    <x:hyperlink ref="B224:B224" r:id="Rdacf951fe1c744c8" display="https://etf.dws.com//en-gb/LU0292103651-msci-europe-financials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B225:B225" r:id="R60c3171e38d54b1b" display="https://etf.dws.com//en-gb/LU0292104030-msci-europe-communication-services-ucits-etf-1c/"/>
+    <x:hyperlink ref="B226:B226" r:id="Rcce213e21c2d499e" display="https://etf.dws.com//en-gb/LU0292104469-msci-europe-information-technology-ucits-etf-1c/"/>
+    <x:hyperlink ref="B227:B227" r:id="R457c8bcfd1f543cd" display="https://etf.dws.com//en-gb/LU0292104899-msci-europe-utilities-ucits-etf-1c/"/>
+    <x:hyperlink ref="B228:B228" r:id="R1b1732c7569e4fd4" display="https://etf.dws.com//en-gb/LU0292105359-msci-europe-consumer-staples-ucits-etf-1c/"/>
+    <x:hyperlink ref="B229:B229" r:id="Rc9f985f7e3a540fe" display="https://etf.dws.com//en-gb/LU0292106084-msci-europe-industrials-ucits-etf-1c/"/>
+    <x:hyperlink ref="B230:B230" r:id="R6d1338ff359e47ae" display="https://etf.dws.com//en-gb/LU0292106167-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B231:B231" r:id="R0acc42d12bc94de1" display="https://etf.dws.com//en-gb/LU0292106241-shortdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B232:B232" r:id="R5f66dca569fe4c17" display="https://etf.dws.com//en-gb/LU0292106753-euro-stoxx-50-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B233:B233" r:id="R54e1da5c4d1443d6" display="https://etf.dws.com//en-gb/LU0292107645-msci-emerging-markets-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B234:B234" r:id="R45045cc730aa46c9" display="https://etf.dws.com//en-gb/LU0292107991-msci-em-asia-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B235:B235" r:id="R58a50af5510849b6" display="https://etf.dws.com//en-gb/LU0292108619-msci-em-latin-america-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B236:B236" r:id="Rb290f54e0a134212" display="https://etf.dws.com//en-gb/LU0292109005-msci-em-europe-middle-east-africa-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B237:B237" r:id="R81daf82cdb884c1b" display="https://etf.dws.com//en-gb/LU0292109187-msci-taiwan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B238:B238" r:id="R2466910858024136" display="https://etf.dws.com//en-gb/LU0292109344-msci-brazil-ucits-etf-1c/"/>
+    <x:hyperlink ref="B239:B239" r:id="R0b75e64939ad457c" display="https://etf.dws.com//en-gb/LU0292109690-nifty-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B240:B240" r:id="R886eba8b7a1343ad" display="https://etf.dws.com//en-gb/LU0292109856-msci-china-a-ucits-etf-1c/"/>
+    <x:hyperlink ref="B241:B241" r:id="R13a6cff722354f97" display="https://etf.dws.com//en-gb/LU0321462870-itraxx-crossover-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B242:B242" r:id="R81c14aa56a494428" display="https://etf.dws.com//en-gb/LU0321462953-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B243:B243" r:id="Rf5d80112e6cf4b9b" display="https://etf.dws.com//en-gb/LU0321464652-gbp-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B244:B244" r:id="R7a7f436b55374e47" display="https://etf.dws.com//en-gb/LU0321465469-usd-overnight-rate-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B245:B245" r:id="Rc0c67cff73134088" display="https://etf.dws.com//en-gb/LU0322248146-sli-ucits-etf-1d/"/>
+    <x:hyperlink ref="B246:B246" r:id="Rd07e81ee396b4d5a" display="https://etf.dws.com//en-gb/LU0322250712-lpx-private-equity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B247:B247" r:id="R303c6fd10ae4444e" display="https://etf.dws.com//en-gb/LU0322250985-cac-40-ucits-etf-1d/"/>
+    <x:hyperlink ref="B248:B248" r:id="R0e7ed3d97fc649bf" display="https://etf.dws.com//en-gb/LU0322251520-s-p-500-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B249:B249" r:id="Rb61f88a6a9344579" display="https://etf.dws.com//en-gb/LU0322252171-msci-ac-asia-ex-japan-esg-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B250:B250" r:id="R92cea6adc3a24bb1" display="https://etf.dws.com//en-gb/LU0322252338-msci-pacific-ex-japan-ucits-etf-1c/"/>
+    <x:hyperlink ref="B251:B251" r:id="Rc53d9c029552487d" display="https://etf.dws.com//en-gb/LU0322252924-vietnam-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B252:B252" r:id="Rb8913493163b4eaf" display="https://etf.dws.com//en-gb/LU0322253229-s-p-global-infrastructure-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B253:B253" r:id="R0c221bce1eb04ba9" display="https://etf.dws.com//en-gb/LU0322253732-msci-europe-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B254:B254" r:id="Rc04d2b5a2ac5421a" display="https://etf.dws.com//en-gb/LU0322253906-msci-europe-small-cap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B255:B255" r:id="Rbc118e2a56004f2c" display="https://etf.dws.com//en-gb/LU0328473581-ftse-100-short-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B256:B256" r:id="R236247a944394440" display="https://etf.dws.com//en-gb/LU0328474803-s-p-asx-200-ucits-etf-1d/"/>
+    <x:hyperlink ref="B257:B257" r:id="R5f045a343f0d4f37" display="https://etf.dws.com//en-gb/LU0328475792-stoxx-europe-600-ucits-etf-1c/"/>
+    <x:hyperlink ref="B258:B258" r:id="R031a559eba444aab" display="https://etf.dws.com//en-gb/LU0328476410-s-p-select-frontier-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B259:B259" r:id="R66e5bc1de1404f49" display="https://etf.dws.com//en-gb/LU0335044896-eur-overnight-rate-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B260:B260" r:id="Rd454888b9f5748a2" display="https://etf.dws.com//en-gb/LU0378818131-global-government-bond-ucits-etf-1c-eur-hedged/"/>
+    <x:hyperlink ref="B261:B261" r:id="R612d7064e86d4740" display="https://etf.dws.com//en-gb/LU0378818560-singapore-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B262:B262" r:id="Re995175899af40d2" display="https://etf.dws.com//en-gb/LU0380865021-euro-stoxx-50-ucits-etf-1c/"/>
+    <x:hyperlink ref="B263:B263" r:id="R66a7158273ea433b" display="https://etf.dws.com//en-gb/LU0397221945-portfolio-ucits-etf-1c/"/>
+    <x:hyperlink ref="B264:B264" r:id="R7c0896c1504c4318" display="https://etf.dws.com//en-gb/LU0411075020-shortdax-x2-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B265:B265" r:id="R2997dffa136d49e2" display="https://etf.dws.com//en-gb/LU0411075376-levdax-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B266:B266" r:id="R2a3c67a153914c02" display="https://etf.dws.com//en-gb/LU0411078552-s-p-500-2x-leveraged-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B267:B267" r:id="R9ce9b503a07b4f42" display="https://etf.dws.com//en-gb/LU0411078636-s-p-500-2x-inverse-daily-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B268:B268" r:id="R0b64d1178fc948db" display="https://etf.dws.com//en-gb/LU0429458895-us-treasuries-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B269:B269" r:id="Ree17a10076ac4c43" display="https://etf.dws.com//en-gb/LU0429459356-us-treasuries-ucits-etf-1d/"/>
+    <x:hyperlink ref="B270:B270" r:id="R8855e541bb1a4fb2" display="https://etf.dws.com//en-gb/LU0429790743-bloomberg-commodity-swap-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B271:B271" r:id="Refcc9bc8b71c48e0" display="https://etf.dws.com//en-gb/LU0460391732-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-2c/"/>
+    <x:hyperlink ref="B272:B272" r:id="R0ab02d5c34e04a06" display="https://etf.dws.com//en-gb/LU0460391906-bloomberg-commodity-ex-agriculture-livestock-swap-ucits-etf-3c-gbp-hedged/"/>
+    <x:hyperlink ref="B273:B273" r:id="R94113e1557894631" display="https://etf.dws.com//en-gb/LU0468896575-germany-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B274:B274" r:id="Rfe860c556edd426e" display="https://etf.dws.com//en-gb/LU0468897110-germany-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B275:B275" r:id="R9fb5a8ce70b446f5" display="https://etf.dws.com//en-gb/LU0476289466-msci-mexico-ucits-etf-1c/"/>
+    <x:hyperlink ref="B276:B276" r:id="Rfb6c1889a085407a" display="https://etf.dws.com//en-gb/LU0476289540-msci-canada-screened-ucits-etf-1c/"/>
+    <x:hyperlink ref="B277:B277" r:id="R6763f1f038ea4c51" display="https://etf.dws.com//en-gb/LU0476289623-msci-indonesia-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B278:B278" r:id="R2c23bd3ade2a4944" display="https://etf.dws.com//en-gb/LU0478205379-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B279:B279" r:id="R6c2d935626624e8b" display="https://etf.dws.com//en-gb/LU0478205965-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B280:B280" r:id="R77dcc248ac8b412c" display="https://etf.dws.com//en-gb/LU0484968812-eur-corporate-bond-sri-pab-ucits-etf-1d/"/>
+    <x:hyperlink ref="B281:B281" r:id="Ra60fbd716bfd4288" display="https://etf.dws.com//en-gb/LU0484968903-eur-corporate-bond-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B282:B282" r:id="Rb9936a69ce9d40b1" display="https://etf.dws.com//en-gb/LU0484969463-target-maturity-sept-2029-italy-and-spain-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B283:B283" r:id="Rec6c2cf9221b4e9f" display="https://etf.dws.com//en-gb/LU0486851024-msci-europe-value-ucits-etf-1c/"/>
+    <x:hyperlink ref="B284:B284" r:id="Rce96e06bc60243ff" display="https://etf.dws.com//en-gb/LU0489337690-ftse-developed-europe-real-estate-ucits-etf-1c/"/>
+    <x:hyperlink ref="B285:B285" r:id="Rfeda9f9f9e0f4711" display="https://etf.dws.com//en-gb/LU0490618542-s-p-500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B286:B286" r:id="Rc6b6d01a5a5c4620" display="https://etf.dws.com//en-gb/LU0494592974-australia-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B287:B287" r:id="R29c50b6f5bd74b50" display="https://etf.dws.com//en-gb/LU0514694370-msci-malaysia-ucits-etf-1c/"/>
+    <x:hyperlink ref="B288:B288" r:id="R529b4cc3048f4cc8" display="https://etf.dws.com//en-gb/LU0514694701-msci-thailand-ucits-etf-1c/"/>
+    <x:hyperlink ref="B289:B289" r:id="R4313c3efbaa34fc9" display="https://etf.dws.com//en-gb/LU0514695187-msci-india-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B290:B290" r:id="R5363c5cd2e2b4a2c" display="https://etf.dws.com//en-gb/LU0514695690-msci-china-ucits-etf-1c/"/>
+    <x:hyperlink ref="B291:B291" r:id="R470efad5430f417d" display="https://etf.dws.com//en-gb/LU0524480265-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1c/"/>
+    <x:hyperlink ref="B292:B292" r:id="R0bef838d01764259" display="https://etf.dws.com//en-gb/LU0592215403-msci-philippines-ucits-etf-1c/"/>
+    <x:hyperlink ref="B293:B293" r:id="Reb6b492645974c0b" display="https://etf.dws.com//en-gb/LU0592216393-spain-ucits-etf-1c/"/>
+    <x:hyperlink ref="B294:B294" r:id="Rde1aa7cbe8d84b86" display="https://etf.dws.com//en-gb/LU0592217524-msci-africa-top-50-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B295:B295" r:id="Rd658d78e4b964963" display="https://etf.dws.com//en-gb/LU0613540268-italy-government-bond-0-1-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B296:B296" r:id="R0e1ff767369e49d4" display="https://etf.dws.com//en-gb/LU0614173549-eurozone-government-bond-1-3-ucits-etf-1d/"/>
+    <x:hyperlink ref="B297:B297" r:id="Rde0eb47d696f4f9f" display="https://etf.dws.com//en-gb/LU0614173895-eurozone-government-bond-3-5-ucits-etf-1d/"/>
+    <x:hyperlink ref="B298:B298" r:id="R1b3727c8dda6433a" display="https://etf.dws.com//en-gb/LU0641006290-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B299:B299" r:id="R73c0d594a5e64f70" display="https://etf.dws.com//en-gb/LU0641006456-global-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B300:B300" r:id="R85e77b733ca649c5" display="https://etf.dws.com//en-gb/LU0641006613-global-government-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B301:B301" r:id="R6572a01cf0434a1c" display="https://etf.dws.com//en-gb/LU0641007009-global-inflation-linked-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B302:B302" r:id="Rdf48f5229f7b4af1" display="https://etf.dws.com//en-gb/LU0641007264-global-inflation-linked-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B303:B303" r:id="R8653127cb8434f9e" display="https://etf.dws.com//en-gb/LU0641007421-global-inflation-linked-bond-ucits-etf-4d-chf-hedged/"/>
+    <x:hyperlink ref="B304:B304" r:id="R71e02ef324f14587" display="https://etf.dws.com//en-gb/LU0643975161-germany-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B305:B305" r:id="R27998342520042de" display="https://etf.dws.com//en-gb/LU0643975591-eurozone-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B306:B306" r:id="R39f1516313f743e2" display="https://etf.dws.com//en-gb/LU0659578842-msci-singapore-ucits-etf-1c/"/>
+    <x:hyperlink ref="B307:B307" r:id="R1b80621e09c4464e" display="https://etf.dws.com//en-gb/LU0659579063-atx-ucits-etf-1c/"/>
+    <x:hyperlink ref="B308:B308" r:id="R0385e7a843e64725" display="https://etf.dws.com//en-gb/LU0659579147-msci-pakistan-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B309:B309" r:id="R9ef56f336011468b" display="https://etf.dws.com//en-gb/LU0659579733-msci-world-swap-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B310:B310" r:id="R631bd7086ee04f84" display="https://etf.dws.com//en-gb/LU0659580079-msci-japan-ucits-etf-4c-eur-hedged/"/>
+    <x:hyperlink ref="B311:B311" r:id="R5e7a3283177f41ff" display="https://etf.dws.com//en-gb/LU0677077884-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2d/"/>
+    <x:hyperlink ref="B312:B312" r:id="Rad424370230c4e2c" display="https://etf.dws.com//en-gb/LU0690964092-global-government-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B313:B313" r:id="R4b8156e090774853" display="https://etf.dws.com//en-gb/LU0779800910-csi300-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B314:B314" r:id="R77659760c5b948e1" display="https://etf.dws.com//en-gb/LU0838780707-ftse-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B315:B315" r:id="R848f0c7ff74544b2" display="https://etf.dws.com//en-gb/LU0838782315-dax-esg-screened-ucits-etf-1d/"/>
+    <x:hyperlink ref="B316:B316" r:id="Ra29fb43db8324da7" display="https://etf.dws.com//en-gb/LU0839027447-nikkei-225-ucits-etf-1d/"/>
+    <x:hyperlink ref="B317:B317" r:id="Rf8bb8d7efae341c3" display="https://etf.dws.com//en-gb/LU0846194776-msci-emu-ucits-etf-1d/"/>
+    <x:hyperlink ref="B318:B318" r:id="R8cada200483c4cb8" display="https://etf.dws.com//en-gb/LU0875160326-harvest-csi300-ucits-etf-1d/"/>
+    <x:hyperlink ref="B319:B319" r:id="R2ae7229fa62b470a" display="https://etf.dws.com//en-gb/LU0908508731-global-government-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B320:B320" r:id="Rfcf3dde0fd0a4878" display="https://etf.dws.com//en-gb/LU0908508814-global-inflation-linked-bond-ucits-etf-5c/"/>
+    <x:hyperlink ref="B321:B321" r:id="Rc9fd026845cb4cc2" display="https://etf.dws.com//en-gb/LU0925589839-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B322:B322" r:id="Rf457e483cd564468" display="https://etf.dws.com//en-gb/LU0927735406-msci-japan-ucits-etf-2d-usd-hedged/"/>
+    <x:hyperlink ref="B323:B323" r:id="R3e54e073e6a14df6" display="https://etf.dws.com//en-gb/LU0942970103-esg-global-aggregate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B324:B324" r:id="R091504981b514872" display="https://etf.dws.com//en-gb/LU0942970285-esg-global-aggregate-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B325:B325" r:id="R88919f9d769441d9" display="https://etf.dws.com//en-gb/LU0942970368-esg-global-aggregate-bond-ucits-etf-3d-gbp-hedged/"/>
+    <x:hyperlink ref="B326:B326" r:id="Rd400734c4a274725" display="https://etf.dws.com//en-gb/LU0942970442-esg-global-aggregate-bond-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B327:B327" r:id="R90a64eac11484acd" display="https://etf.dws.com//en-gb/LU0942970798-esg-global-aggregate-bond-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B328:B328" r:id="R69c8ddd288c04b4b" display="https://etf.dws.com//en-gb/LU0943504760-switzerland-ucits-etf-1c/"/>
+    <x:hyperlink ref="B329:B329" r:id="R494b43f3a1464dd6" display="https://etf.dws.com//en-gb/LU0952581584-japan-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B330:B330" r:id="R802218d3685142c7" display="https://etf.dws.com//en-gb/LU0962071741-iboxx-eurozone-government-bond-yield-plus-ucits-etf-1d/"/>
+    <x:hyperlink ref="B331:B331" r:id="R00434e1246154c95" display="https://etf.dws.com//en-gb/LU0962078753-global-inflation-linked-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B332:B332" r:id="Rffc6a1ea5c0f4c25" display="https://etf.dws.com//en-gb/LU0994505336-spain-ucits-etf-1d/"/>
+    <x:hyperlink ref="B333:B333" r:id="Rb5d6209c197d4d98" display="https://etf.dws.com//en-gb/LU1094612022-harvest-china-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B334:B334" r:id="Rb64bd072656743ae" display="https://etf.dws.com//en-gb/LU1109939865-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1d/"/>
+    <x:hyperlink ref="B335:B335" r:id="R31cb00bb197c43de" display="https://etf.dws.com//en-gb/LU1109941689-rolling-target-maturity-sept-2027-eur-high-yield-ucits-etf-1c/"/>
+    <x:hyperlink ref="B336:B336" r:id="R5cdf3fe2a6684c0d" display="https://etf.dws.com//en-gb/LU1109942653-eur-high-yield-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B337:B337" r:id="R3ef2d31b6a794663" display="https://etf.dws.com//en-gb/LU1109943388-eur-high-yield-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B338:B338" r:id="R853dd1b5a5824bc0" display="https://etf.dws.com//en-gb/LU1127514245-msci-emu-ucits-etf-1c-usd-hedged/"/>
+    <x:hyperlink ref="B339:B339" r:id="Rb121c08075b040a7" display="https://etf.dws.com//en-gb/LU1127516455-msci-emu-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B340:B340" r:id="R53cac4a6c06344c2" display="https://etf.dws.com//en-gb/LU1184092051-msci-europe-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B341:B341" r:id="R037503a504394819" display="https://etf.dws.com//en-gb/LU1215827756-msci-japan-ucits-etf-7c-chf-hedged/"/>
+    <x:hyperlink ref="B342:B342" r:id="R301c7edd50fb4b39" display="https://etf.dws.com//en-gb/LU1215828218-msci-emu-ucits-etf-3c-chf-hedged/"/>
+    <x:hyperlink ref="B343:B343" r:id="Rdc86be178d884d56" display="https://etf.dws.com//en-gb/LU1221100792-dax-esg-screened-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B344:B344" r:id="R2752d82f9eb34046" display="https://etf.dws.com//en-gb/LU1221102491-dax-esg-screened-ucits-etf-4c-chf-hedged/"/>
+    <x:hyperlink ref="B345:B345" r:id="R35491701c5884a17" display="https://etf.dws.com//en-gb/LU1242369327-msci-europe-ucits-etf-1d/"/>
+    <x:hyperlink ref="B346:B346" r:id="Ra9198488c1094fcc" display="https://etf.dws.com//en-gb/LU1310477036-harvest-csi-a500-ucits-etf-1d/"/>
+    <x:hyperlink ref="B347:B347" r:id="R8d86cf0b68894685" display="https://etf.dws.com//en-gb/LU1349386927-dax-ucits-etf-1d/"/>
+    <x:hyperlink ref="B348:B348" r:id="Rc2fd039b5b694ec1" display="https://etf.dws.com//en-gb/LU1399300455-us-treasuries-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B349:B349" r:id="Rde8c3efe71804992" display="https://etf.dws.com//en-gb/LU1772333404-stoxx-europe-600-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B350:B350" r:id="R57b1bd96946645d7" display="https://etf.dws.com//en-gb/LU1875395870-nikkei-225-ucits-etf-2d-eur-hedged/"/>
+    <x:hyperlink ref="B351:B351" r:id="Rdecd3a5b17394ae0" display="https://etf.dws.com//en-gb/LU1920015440-j-p-morgan-usd-emerging-markets-bond-ucits-etf-2c/"/>
+    <x:hyperlink ref="B352:B352" r:id="Rf4df92c015204ecd" display="https://etf.dws.com//en-gb/LU1920015523-us-treasuries-1-3-ucits-etf-1c/"/>
+    <x:hyperlink ref="B353:B353" r:id="Rf6e9ab25a68a4be1" display="https://etf.dws.com//en-gb/LU1920015796-us-treasuries-ucits-etf-1c/"/>
+    <x:hyperlink ref="B354:B354" r:id="Re3396d13fd2d45fb" display="https://etf.dws.com//en-gb/LU2009147591-eurozone-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B355:B355" r:id="Rccff38d7798b4cb7" display="https://etf.dws.com//en-gb/LU2009147757-s-p-500-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B356:B356" r:id="R37031fbed76a45b9" display="https://etf.dws.com//en-gb/LU2158769930-j-p-morgan-em-local-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B357:B357" r:id="Rf12d5acf3d654b3d" display="https://etf.dws.com//en-gb/LU2178481649-eur-corporate-bond-short-duration-sri-pab-ucits-etf-1c/"/>
+    <x:hyperlink ref="B358:B358" r:id="R2df56ff875ee4932" display="https://etf.dws.com//en-gb/LU2196470426-nikkei-225-ucits-etf-1c/"/>
+    <x:hyperlink ref="B359:B359" r:id="R0024b609c3504d65" display="https://etf.dws.com//en-gb/LU2196472984-s-p-500-swap-ucits-etf-5c-eur-hedged/"/>
+    <x:hyperlink ref="B360:B360" r:id="R04361f60b68d4995" display="https://etf.dws.com//en-gb/LU2196473016-s-p-500-swap-ucits-etf-7c-gbp-hedged/"/>
+    <x:hyperlink ref="B361:B361" r:id="Ra12a3a66ef514e30" display="https://etf.dws.com//en-gb/LU2263803533-msci-world-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B362:B362" r:id="R5b0c6ad515d445e8" display="https://etf.dws.com//en-gb/LU2278080713-bloomberg-commodity-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B363:B363" r:id="Rc576789e4d294201" display="https://etf.dws.com//en-gb/LU2296661775-msci-em-asia-screened-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B364:B364" r:id="R872ad33c6aac46c3" display="https://etf.dws.com//en-gb/LU2361257269-j-p-morgan-usd-emerging-markets-bond-ucits-etf-1d-eur-hedged/"/>
+    <x:hyperlink ref="B365:B365" r:id="R4a0bf47bbbec48e2" display="https://etf.dws.com//en-gb/LU2376679564-harvest-msci-china-tech-100-ucits-etf-1c/"/>
+    <x:hyperlink ref="B366:B366" r:id="Rc831b8cd0db44411" display="https://etf.dws.com//en-gb/LU2385068163-esg-global-government-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B367:B367" r:id="R17fe239991294484" display="https://etf.dws.com//en-gb/LU2385068247-esg-global-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B368:B368" r:id="R250ab595c92f4868" display="https://etf.dws.com//en-gb/LU2385068320-esg-global-government-bond-ucits-etf-3d-usd-hedged/"/>
+    <x:hyperlink ref="B369:B369" r:id="Rb4caabe5ffe74e4f" display="https://etf.dws.com//en-gb/LU2385068593-esg-global-government-bond-ucits-etf-4d-eur-hedged/"/>
+    <x:hyperlink ref="B370:B370" r:id="R83dd7bbdf88947a6" display="https://etf.dws.com//en-gb/LU2456436083-msci-china-ucits-etf-1d/"/>
+    <x:hyperlink ref="B371:B371" r:id="Rc50c77c662834365" display="https://etf.dws.com//en-gb/LU2462217071-esg-global-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B372:B372" r:id="Re48816c34efa4b18" display="https://etf.dws.com//en-gb/LU2468423459-esg-eurozone-government-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B373:B373" r:id="Rdf12cf45db4a4e00" display="https://etf.dws.com//en-gb/LU2469465822-msci-china-a-screened-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B374:B374" r:id="Rb95fb9b5a6a040f6" display="https://etf.dws.com//en-gb/LU2504532131-tips-us-inflation-linked-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B375:B375" r:id="R6ab11158080a47b2" display="https://etf.dws.com//en-gb/LU2504532487-eurozone-government-green-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B376:B376" r:id="R8539dd94754a4513" display="https://etf.dws.com//en-gb/LU2504537445-eurozone-government-bond-esg-tilted-ucits-etf-1d/"/>
+    <x:hyperlink ref="B377:B377" r:id="Ra816bb327bf14f24" display="https://etf.dws.com//en-gb/LU2523865728-eurozone-government-bond-7-10-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B378:B378" r:id="R008a83c0e5e046ae" display="https://etf.dws.com//en-gb/LU2523865991-eurozone-government-bond-7-10-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B379:B379" r:id="R2baa91fd70194e40" display="https://etf.dws.com//en-gb/LU2523866023-eurozone-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B380:B380" r:id="Rcbd7f6efab9a49a9" display="https://etf.dws.com//en-gb/LU2523866296-germany-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B381:B381" r:id="R2af3707b19c940e8" display="https://etf.dws.com//en-gb/LU2523866379-germany-government-bond-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B382:B382" r:id="Rf61847fdd7504213" display="https://etf.dws.com//en-gb/LU2552296563-iboxx-eurozone-government-bond-yield-plus-1-3-ucits-etf-2d/"/>
+    <x:hyperlink ref="B383:B383" r:id="R6cc71fbd3dce4568" display="https://etf.dws.com//en-gb/LU2581375073-msci-usa-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B384:B384" r:id="Rfa3f89f8ba53421a" display="https://etf.dws.com//en-gb/LU2581375156-stoxx-europe-600-ucits-etf-1d/"/>
+    <x:hyperlink ref="B385:B385" r:id="R5bbccc4caa5041d9" display="https://etf.dws.com//en-gb/LU2581375230-msci-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B386:B386" r:id="R56e9605e295948bd" display="https://etf.dws.com//en-gb/LU2606231335-eurozone-government-bond-3-5-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B387:B387" r:id="R281bb345e33c4f9f" display="https://etf.dws.com//en-gb/LU2606231418-eurozone-government-bond-3-5-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B388:B388" r:id="R45f1b5a483404a98" display="https://etf.dws.com//en-gb/LU2610432036-us-treasuries-ucits-etf-2c-gbp-hedged/"/>
+    <x:hyperlink ref="B389:B389" r:id="Rc4021ef099b24090" display="https://etf.dws.com//en-gb/LU2641054122-eurozone-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B390:B390" r:id="R1ea469d9bbfb4f23" display="https://etf.dws.com//en-gb/LU2641054551-germany-government-bond-0-1-ucits-etf-1c/"/>
+    <x:hyperlink ref="B391:B391" r:id="R1da3e2a1e1d447ae" display="https://etf.dws.com//en-gb/LU2662649412-us-treasuries-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B392:B392" r:id="Rbaba43b1c9ad4479" display="https://etf.dws.com//en-gb/LU2662649503-us-treasuries-3-7-ucits-etf-1d/"/>
+    <x:hyperlink ref="B393:B393" r:id="R02cebef9d36f487c" display="https://etf.dws.com//en-gb/LU2662649685-us-treasuries-7-10-ucits-etf-1d/"/>
+    <x:hyperlink ref="B394:B394" r:id="Rf14cdbb3a8f2450b" display="https://etf.dws.com//en-gb/LU2673522830-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B395:B395" r:id="R3d1821b5457a45d0" display="https://etf.dws.com//en-gb/LU2673522913-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B396:B396" r:id="Rcfb9d4d7be4d42c7" display="https://etf.dws.com//en-gb/LU2673523051-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B397:B397" r:id="Re531d96f6d1a4281" display="https://etf.dws.com//en-gb/LU2673523135-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1c/"/>
+    <x:hyperlink ref="B398:B398" r:id="Rd8a54dfcdee84064" display="https://etf.dws.com//en-gb/LU2673523218-target-maturity-sept-2027-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B399:B399" r:id="R0f4074225f4e41a0" display="https://etf.dws.com//en-gb/LU2673523309-target-maturity-sept-2029-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B400:B400" r:id="Rf93dbcbacb4946f2" display="https://etf.dws.com//en-gb/LU2673523481-target-maturity-sept-2031-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B401:B401" r:id="R5f1f080d6b4d4096" display="https://etf.dws.com//en-gb/LU2673523564-target-maturity-sept-2033-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B402:B402" r:id="R519c29a889774ff5" display="https://etf.dws.com//en-gb/LU2675291913-msci-emerging-markets-swap-ucits-etf-1d/"/>
+    <x:hyperlink ref="B403:B403" r:id="Rbb03b5307e28492d" display="https://etf.dws.com//en-gb/LU2755521270-msci-pacific-ex-japan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B404:B404" r:id="R7f85120a7b9a4a21" display="https://etf.dws.com//en-gb/LU2788421340-csi500-swap-ucits-etf-1c/"/>
+    <x:hyperlink ref="B405:B405" r:id="R1bbb423430384f33" display="https://etf.dws.com//en-gb/LU2809864296-target-maturity-sept-2030-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B406:B406" r:id="Rf0718153dbac4e82" display="https://etf.dws.com//en-gb/LU2809864452-target-maturity-sept-2032-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B407:B407" r:id="Rb471f0c41b7f41c9" display="https://etf.dws.com//en-gb/LU2809864619-target-maturity-sept-2034-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B408:B408" r:id="R06996d7d397645b1" display="https://etf.dws.com//en-gb/LU2810185665-target-maturity-sept-2028-eur-corporate-bond-ucits-etf-1d/"/>
+    <x:hyperlink ref="B409:B409" r:id="Rbd346cf6afab4539" display="https://etf.dws.com//en-gb/LU2859297330-world-small-cap-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B410:B410" r:id="Rcd86831e4e60473f" display="https://etf.dws.com//en-gb/LU2859392081-world-green-tech-innovators-ucits-etf-1c/"/>
+    <x:hyperlink ref="B411:B411" r:id="Rb0bb8d28bb3c475e" display="https://etf.dws.com//en-gb/LU2903252349-scalable-msci-ac-world-xtrackers-ucits-etf-1c/"/>
+    <x:hyperlink ref="B412:B412" r:id="R293a440f6e9c4943" display="https://etf.dws.com//en-gb/LU2928641757-msci-taiwan-ucits-etf-1d/"/>
+    <x:hyperlink ref="B413:B413" r:id="Rbb998d9a1e3f4bc4" display="https://etf.dws.com//en-gb/LU3003217554-eurozone-government-bond-1-3-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B414:B414" r:id="Raeb1f44a3b26417c" display="https://etf.dws.com//en-gb/LU3003217638-eurozone-government-bond-1-3-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B415:B415" r:id="Ra41153c4b0bd4cce" display="https://etf.dws.com//en-gb/LU3003217711-eurozone-government-bond-5-7-ucits-etf-2c-usd-hedged/"/>
+    <x:hyperlink ref="B416:B416" r:id="R71c666341add4965" display="https://etf.dws.com//en-gb/LU3003217984-eurozone-government-bond-5-7-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B417:B417" r:id="Rdb3d56fafb2448c1" display="https://etf.dws.com//en-gb/LU3003218016-australia-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B418:B418" r:id="R59d82dc3a59c48d2" display="https://etf.dws.com//en-gb/LU3003218107-australia-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B419:B419" r:id="R14f918a7b0bd4ac2" display="https://etf.dws.com//en-gb/LU3003218362-australia-government-bond-ucits-etf-1d-gbp-hedged/"/>
+    <x:hyperlink ref="B420:B420" r:id="R1065cdd04c514664" display="https://etf.dws.com//en-gb/LU3003218446-japan-government-bond-ucits-etf-2c-eur-hedged/"/>
+    <x:hyperlink ref="B421:B421" r:id="R0d0684d1f30a47a6" display="https://etf.dws.com//en-gb/LU3003218792-japan-government-bond-ucits-etf-3c-usd-hedged/"/>
+    <x:hyperlink ref="B422:B422" r:id="R6d4b46406e464020" display="https://etf.dws.com//en-gb/LU3003218958-japan-government-bond-ucits-etf-2d-gbp-hedged/"/>
+    <x:hyperlink ref="B423:B423" r:id="Rcc3e79e96ab14b4e" display="https://etf.dws.com//en-gb/LU3061478973-europe-defence-technologies-ucits-etf-1c/"/>
+    <x:hyperlink ref="B424:B424" r:id="Ra31d54107a794fc2" display="https://etf.dws.com//en-gb/LU3116008346-diversified-portfolio-20-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B425:B425" r:id="R19a0df66ccbf4e7a" display="https://etf.dws.com//en-gb/LU3116008429-diversified-portfolio-40-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B426:B426" r:id="Rf03e00fbcd424de8" display="https://etf.dws.com//en-gb/LU3116008692-diversified-portfolio-60-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B427:B427" r:id="Re560d40e38614800" display="https://etf.dws.com//en-gb/LU3116008775-diversified-portfolio-80-equity-ucits-etf-1c/"/>
+    <x:hyperlink ref="B428:B428" r:id="R7550bf246b5d4242" display="https://etf.dws.com//en-gb/LU3121019551-global-government-bond-ucits-etf-3d-chf-hedged/"/>
+    <x:hyperlink ref="B429:B429" r:id="Rb9df951c3b7e4647" display="https://etf.dws.com//en-gb/LU3123443510-salam-usd-global-aggregate-sukuk-ucits-etf-1d/"/>
+    <x:hyperlink ref="B430:B430" r:id="Rf1c4207b91734ad8" display="https://etf.dws.com//en-gb/LU3184977026-msci-world-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B431:B431" r:id="R0630552df4de4fa5" display="https://etf.dws.com//en-gb/LU3184977299-msci-europe-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B432:B432" r:id="R5d03f31710a84506" display="https://etf.dws.com//en-gb/LU3184977372-msci-usa-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B433:B433" r:id="Rb51251fd51c84404" display="https://etf.dws.com//en-gb/LU3184977455-msci-emerging-markets-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B434:B434" r:id="Rcd4068a2055d4778" display="https://etf.dws.com//en-gb/LU3184977612-s-p-500-swap-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B435:B435" r:id="R0942d569ce8d4888" display="https://etf.dws.com//en-gb/LU3184977703-ftse-100-ucits-etf-ic-gbp-unlisted/"/>
+    <x:hyperlink ref="B436:B436" r:id="R92f7028893f04bfb" display="https://etf.dws.com//en-gb/LU3198621024-s-p-500-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B437:B437" r:id="R97f76843aad94936" display="https://etf.dws.com//en-gb/LU3284391318-global-government-bond-ucits-etf-4d/"/>
+    <x:hyperlink ref="B438:B438" r:id="Re531e08a57d14707" display="https://etf.dws.com//en-gb/LU3313127113-eurozone-government-bond-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B439:B439" r:id="R27713e8b63e44aec" display="https://etf.dws.com//en-gb/LU3353962601-msci-world-swap-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B440:B440" r:id="Rf2139b35c86b417f" display="https://etf.dws.com//en-gb/LU3353962783-s-p-500-swap-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B441:B441" r:id="R90792f2d0b9c42a4" display="https://etf.dws.com//en-gb/LU3353962866-stoxx-global-select-dividend-100-swap-ucits-etf-ic-usd-unlisted/"/>
+    <x:hyperlink ref="B442:B442" r:id="Rb84089a05763490c" display="https://etf.dws.com//en-gb/LU3353962940-stoxx-europe-600-ucits-etf-ic-eur-unlisted/"/>
+    <x:hyperlink ref="B443:B443" r:id="Rd22e9589508b4a75" display="https://etf.dws.com//en-gb/LU3370249040-bloomberg-commodity-swap-ucits-etf-3c-gbp-hedged/"/>
+    <x:hyperlink ref="B444:B444" r:id="R350f4e4c1a784c43" display="https://etf.dws.com//en-gb/LU3375213041-msci-world-swap-ucits-etf-ic-usd-unlisted/"/>
   </x:hyperlinks>
   <x:pageMargins left="0.17" right="0.17" top="0.17" bottom="0.17" header="0" footer="0.3"/>
   <x:pageSetup orientation="landscape"/>
   <x:drawing r:id="rId2"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R72755efb6d20477e"/>
+    <x:tablePart r:id="R9e574b5dabce4096"/>
   </x:tableParts>
 </x:worksheet>
 </file>